--- a/data/call-sheets/CornerHelp-Master-Provider-List.xlsx
+++ b/data/call-sheets/CornerHelp-Master-Provider-List.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Master List'!$A$3:$W$47</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Master List'!$A$3:$Y$47</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="288">
   <si>
     <t xml:space="preserve">CornerHelp — master provider call sheet · 44 organizations · all 254 Texas counties</t>
   </si>
@@ -56,12 +56,18 @@
     <t xml:space="preserve">Counties</t>
   </si>
   <si>
+    <t xml:space="preserve">ZIPs</t>
+  </si>
+  <si>
     <t xml:space="preserve">People reached</t>
   </si>
   <si>
     <t xml:space="preserve">Counties served</t>
   </si>
   <si>
+    <t xml:space="preserve">ZIP codes served</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
@@ -119,6 +125,9 @@
     <t xml:space="preserve">Brazoria; Galveston; Harris</t>
   </si>
   <si>
+    <t xml:space="preserve">77001 77002 77003 77004 77005 77006 77007 77008 77009 77010 77011 77012 77013 77014 77015 77016 77017 77018 77019 77020 77021 77022 77023 77024 77025 77026 77027 77028 77029 77030 77031 77032 77033 77034 77035 77036 77037 77038 77039 77040 77041 77042 77043 77044 77045 77046 77047 77048 77049 77050 77051 77052 77053 77054 77055 77056 77057 77058 77059 77060 77061 77062 77063 77064 77065 77066 77067 77068 77069 77070 77071 77072 77073 77074 77075 77076 77077 77078 77079 77080 77081 77082 77083 77084 77085 77086 77087 77088 77089 77090 77091 77092 77093 77094 77095 77096 77098 77099 77205 77206 77207 77208 77210 77215 77217 77218 77219 77220 77221 77222 77223 77224 77225 77226 77227 77228 77230 77231 77233 77234 77235 77236 77237 77238 77240 77241 77242 77243 77244 77245 77248 77249 77251 77252 77253 77254 77255 77256 77257 77258 77259 77261 77262 77263 77265 77266 77267 77268 77269 77270 77271 77272 77273 77274 77275 77277 77279 77280 77282 77284 77287 77288 77289 77290 77291 77292 77293 77325 77336 77338 77339 77345 77346 77347 77373 77375 77377 77379 77383 77388 77389 77391 77396 77401 77402 77410 77411 77413 77422 77429 77430 77433 77444 77447 77449 77450 77477 77480 77484 77486 77491 77492 77493 77494 77501 77502 77503 77504 77505 77506 77507 77508 77510 77511 77512 77515 77516 77517 77518 77520 77521 77522 77523 77530 77531 77532 77534 77536 77539 77541 77542 77546 77547 77549 77550 77551 77552 77553 77554 77562 77563 77565 77566 77568 77571 77572 77573 77574 77577 77578 77581 77583 77584 77586 77587 77588 77590 77591 77592 77598 77617 77623 77650</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gulf Coast Community Services Association</t>
   </si>
   <si>
@@ -140,6 +149,9 @@
     <t xml:space="preserve">Anderson; Collin; Denton; Ellis; Henderson; Hunt; Kaufman; Navarro; Rockwall; Van Zandt</t>
   </si>
   <si>
+    <t xml:space="preserve">75002 75007 75009 75010 75011 75013 75022 75023 75024 75025 75026 75027 75028 75029 75032 75033 75034 75035 75036 75048 75056 75057 75065 75067 75068 75069 75070 75071 75072 75074 75075 75077 75078 75080 75082 75086 75087 75088 75089 75093 75094 75098 75102 75103 75105 75109 75110 75114 75117 75119 75124 75125 75126 75127 75135 75140 75142 75143 75144 75147 75148 75151 75152 75153 75154 75155 75156 75157 75158 75159 75160 75161 75163 75165 75166 75167 75168 75169 75173 75189 75252 75287 75370 75379 75401 75402 75403 75404 75407 75409 75422 75423 75424 75428 75442 75449 75452 75453 75454 75469 75474 75495 75496 75751 75752 75754 75756 75758 75763 75770 75778 75779 75790 75801 75802 75803 75832 75839 75844 75853 75859 75861 76041 76052 76064 76065 76078 76084 76177 76201 76202 76205 76206 76207 76208 76209 76210 76226 76227 76247 76249 76258 76259 76262 76266 76626 76639 76641 76648 76651 76670 76679 76681 76693</t>
+  </si>
+  <si>
     <t xml:space="preserve">Texoma Council of Governments</t>
   </si>
   <si>
@@ -155,6 +167,27 @@
     <t xml:space="preserve">Bowie; Camp; Cass; Collin; Cooke; Delta; Denton; Fannin; Franklin; Grayson; Hopkins; Hunt; Lamar; Marion; Morris; Rains; Red River; Rockwall; Titus</t>
   </si>
   <si>
+    <t xml:space="preserve">75002 75007 75009 75010 75011 75013 75020 75021 75022 75023 75024 75025 75026 75027 75028 75029 75032 75033 75034 75035 75036 75048 75056 75057 75058 75065 75067 75068 75069 75070 75071 75072 75074 75075 75076 75077 75078 75080 75082 75086 75087 75088 75089 75090 75091 75092 75093 75094 75098 75135 75160 75166 75169 75173 75189 75252 75287 75370 75379 75401 75402 75403 75404 75407 75409 75410 75411 75412 75414 75415 75416 75417 75418 75420 75421 75422 75423 75424 75426 75428 75431 75432 75433 75435 75436 75437 75438 75439 75440 75441 75442 75446 75447 75448 75449 75450 75451 75452 75453 75454 75455 75456 75457 75459 75460 75461 75462 75468 75469 75470 75471 75472 75473 75474 75476 75477 75478 75479 75480 75481 75482 75483 75486 75487 75488 75489 75490 75491 75492 75494 75495 75496 75497 75501 75503 75504 75505 75550 75551 75554 75555 75556 75558 75559 75560 75561 75562 75563 75564 75566 75567 75568 75569 75570 75571 75572 75574 75630 75638 75656 75657 75668 75683 75686 76052 76078 76177 76201 76202 76205 76206 76207 76208 76209 76210 76226 76227 76233 76238 76239 76240 76241 76245 76247 76249 76250 76252 76253 76258 76259 76262 76263 76264 76265 76266 76271 76272 76273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community Council of Greater Dallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12148715065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75001 75006 75007 75011 75014 75015 75016 75017 75019 75030 75038 75039 75040 75041 75042 75043 75044 75045 75046 75047 75048 75049 75050 75051 75052 75053 75054 75060 75061 75062 75063 75080 75081 75082 75083 75085 75088 75089 75104 75106 75115 75116 75123 75134 75137 75138 75141 75146 75149 75150 75154 75159 75172 75180 75181 75182 75185 75187 75201 75202 75203 75204 75205 75206 75207 75208 75209 75210 75211 75212 75214 75215 75216 75217 75218 75219 75220 75221 75222 75223 75224 75225 75226 75227 75228 75229 75230 75231 75232 75233 75234 75235 75236 75237 75238 75240 75241 75242 75243 75244 75246 75247 75248 75249 75250 75251 75253 75254 75313 75315 75336 75339 75342 75354 75355 75356 75357 75360 75367 75371 75372 75374 75376 75378 75380 75381 75382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas County Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12148191848</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alamo Area Council of Governments</t>
   </si>
   <si>
@@ -167,19 +200,7 @@
     <t xml:space="preserve">Atascosa; Bandera; Bexar; Comal; Frio; Gillespie; Guadalupe; Karnes; Kendall; Kerr; Medina; Wilson</t>
   </si>
   <si>
-    <t xml:space="preserve">Community Council of Greater Dallas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+12148715065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas County Department of Health and Human Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+12148191848</t>
+    <t xml:space="preserve">78002 78003 78004 78005 78006 78008 78009 78010 78011 78012 78013 78015 78016 78017 78023 78024 78025 78026 78027 78028 78029 78039 78050 78052 78054 78055 78056 78057 78058 78059 78061 78062 78063 78064 78065 78066 78069 78070 78073 78074 78101 78108 78109 78111 78112 78113 78114 78115 78116 78117 78118 78119 78121 78123 78124 78130 78131 78132 78133 78140 78141 78147 78148 78150 78151 78152 78154 78155 78156 78160 78161 78163 78201 78202 78203 78204 78205 78206 78207 78208 78209 78210 78211 78212 78213 78214 78215 78216 78217 78218 78219 78220 78221 78222 78223 78224 78225 78226 78227 78228 78229 78230 78231 78232 78233 78234 78235 78236 78237 78238 78239 78240 78242 78244 78245 78246 78247 78248 78249 78250 78251 78252 78253 78254 78255 78256 78257 78258 78259 78260 78261 78263 78264 78265 78266 78268 78269 78270 78278 78279 78280 78283 78284 78288 78291 78292 78293 78294 78295 78296 78297 78298 78299 78618 78623 78624 78631 78638 78648 78655 78670 78671 78675 78850 78861 78883 78884 78885 78886</t>
   </si>
   <si>
     <t xml:space="preserve">Greater East Texas Community Action Program (GETCAP)</t>
@@ -194,6 +215,9 @@
     <t xml:space="preserve">Anderson; Angelina; Chambers; Cherokee; Galveston; Gregg; Hardin; Harrison; Henderson; Houston; Jasper; Jefferson; Kaufman; Liberty; Nacogdoches; Newton; Orange; Panola; Polk; Rusk; Sabine; San Augustine; San Jacinto; Shelby; Smith; Trinity; Tyler; Upshur; Van Zandt; Wood</t>
   </si>
   <si>
+    <t xml:space="preserve">75103 75114 75117 75124 75126 75127 75140 75142 75143 75147 75148 75156 75157 75158 75159 75160 75161 75163 75169 75410 75431 75494 75497 75601 75602 75603 75604 75605 75606 75607 75608 75615 75631 75633 75639 75640 75642 75643 75644 75645 75647 75650 75651 75652 75654 75660 75661 75662 75663 75666 75667 75669 75670 75671 75672 75681 75683 75684 75686 75688 75691 75692 75693 75701 75702 75703 75704 75705 75706 75707 75708 75709 75710 75711 75712 75713 75750 75751 75752 75754 75755 75756 75757 75758 75759 75760 75762 75763 75764 75765 75766 75770 75771 75773 75778 75779 75783 75784 75785 75789 75790 75791 75792 75801 75802 75803 75832 75835 75839 75844 75845 75847 75851 75853 75856 75861 75862 75865 75901 75902 75903 75904 75915 75925 75926 75928 75929 75930 75931 75932 75933 75935 75936 75937 75938 75939 75941 75942 75943 75944 75946 75948 75949 75951 75954 75956 75959 75960 75961 75963 75964 75965 75966 75968 75969 75972 75973 75974 75975 75976 75977 75979 75980 77320 77327 77328 77331 77335 77351 77358 77359 77360 77364 77371 77372 77376 77378 77399 77510 77511 77514 77517 77518 77519 77523 77533 77535 77538 77539 77546 77549 77550 77551 77552 77553 77554 77560 77563 77564 77565 77568 77573 77574 77575 77580 77585 77590 77591 77592 77597 77611 77612 77613 77616 77617 77619 77622 77623 77624 77625 77627 77629 77630 77631 77632 77639 77640 77641 77642 77643 77650 77651 77655 77656 77657 77659 77660 77662 77663 77664 77665 77670 77701 77702 77703 77704 77705 77706 77707 77708 77713 77720 77725 77726</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fort Worth, City of, Neighborhood Services Department</t>
   </si>
   <si>
@@ -206,6 +230,9 @@
     <t xml:space="preserve">Tarrant</t>
   </si>
   <si>
+    <t xml:space="preserve">75050 75051 75052 75053 75054 75261 76001 76002 76003 76004 76005 76006 76007 76008 76010 76011 76012 76013 76014 76015 76016 76017 76018 76020 76021 76022 76028 76034 76036 76039 76040 76051 76052 76053 76054 76060 76063 76071 76092 76094 76095 76096 76099 76101 76102 76103 76104 76105 76106 76107 76108 76109 76110 76111 76112 76113 76114 76115 76116 76117 76118 76119 76120 76121 76123 76124 76126 76127 76131 76132 76133 76134 76135 76136 76137 76140 76147 76148 76155 76161 76162 76163 76164 76177 76179 76180 76182 76185 76244 76248 76262</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bexar County Department of Community Resources</t>
   </si>
   <si>
@@ -215,6 +242,9 @@
     <t xml:space="preserve">Bexar</t>
   </si>
   <si>
+    <t xml:space="preserve">78002 78006 78015 78023 78039 78052 78054 78069 78073 78101 78109 78112 78148 78150 78152 78154 78201 78202 78203 78204 78205 78206 78207 78208 78209 78210 78211 78212 78213 78214 78215 78216 78217 78218 78219 78220 78221 78222 78223 78224 78225 78226 78227 78228 78229 78230 78231 78232 78233 78234 78235 78236 78237 78238 78239 78240 78242 78244 78245 78246 78247 78248 78249 78250 78251 78252 78253 78254 78255 78256 78257 78258 78259 78260 78261 78263 78264 78265 78266 78268 78269 78270 78278 78279 78280 78283 78284 78288 78291 78292 78293 78294 78295 78296 78297 78298 78299</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Antonio, City of, Department of Human Services</t>
   </si>
   <si>
@@ -233,6 +263,9 @@
     <t xml:space="preserve">Bee; Brooks; Cameron; Duval; Hidalgo; Jim Hogg; Jim Wells; Kenedy; Kleberg; San Patricio; Starr; Webb; Willacy; Zapata</t>
   </si>
   <si>
+    <t xml:space="preserve">78019 78040 78041 78042 78043 78044 78045 78046 78067 78076 78102 78104 78119 78125 78142 78146 78162 78332 78335 78336 78338 78341 78344 78349 78352 78353 78355 78357 78359 78360 78361 78362 78363 78368 78369 78370 78371 78372 78374 78375 78376 78379 78383 78384 78385 78387 78389 78390 78391 78501 78502 78503 78504 78505 78516 78520 78521 78522 78523 78526 78535 78536 78537 78538 78539 78540 78541 78542 78543 78545 78547 78548 78550 78551 78552 78553 78557 78559 78560 78561 78562 78563 78564 78566 78569 78570 78572 78573 78574 78575 78576 78577 78578 78579 78580 78582 78583 78584 78586 78588 78589 78591 78593 78595 78596 78597 78598 78599</t>
+  </si>
+  <si>
     <t xml:space="preserve">Combined Community Action, Inc.</t>
   </si>
   <si>
@@ -245,6 +278,45 @@
     <t xml:space="preserve">Austin; Bastrop; Blanco; Caldwell; Colorado; Fayette; Fort Bend; Hays; Lee; Wharton</t>
   </si>
   <si>
+    <t xml:space="preserve">77053 77083 77406 77407 77412 77417 77418 77420 77423 77426 77430 77434 77435 77437 77441 77442 77444 77448 77450 77451 77453 77454 77455 77459 77461 77467 77469 77470 77471 77474 77475 77477 77478 77479 77481 77485 77487 77488 77489 77494 77496 77497 77498 77545 77583 77584 77853 78602 78606 78610 78612 78616 78617 78619 78620 78621 78632 78635 78636 78640 78644 78648 78650 78652 78655 78656 78659 78661 78662 78663 78666 78667 78676 78737 78931 78932 78933 78934 78935 78938 78940 78941 78942 78943 78944 78945 78946 78947 78948 78949 78950 78951 78952 78953 78954 78956 78957 78959 78962 78963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City of Austin Health and Human Services Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+15129725000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78610 78613 78615 78617 78620 78621 78641 78645 78652 78653 78660 78664 78669 78691 78701 78702 78703 78704 78705 78708 78709 78711 78714 78715 78716 78718 78719 78720 78721 78722 78723 78724 78725 78726 78727 78728 78729 78730 78731 78732 78733 78734 78735 78736 78737 78738 78739 78741 78742 78744 78745 78746 78747 78748 78749 78750 78751 78752 78753 78754 78755 78756 78757 78758 78759 78760 78761 78762 78763 78764 78765 78766 78767 78768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travis County Health &amp; Human Services/Veterans Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+15128547250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hill Country Community Action Association, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Saba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+13253725167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bell; Burnet; Coryell; Erath; Hamilton; Lampasas; Llano; Mason; Milam; Mills; San Saba; Somervell; Williamson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76043 76070 76077 76401 76433 76436 76445 76446 76453 76457 76462 76463 76465 76501 76502 76503 76504 76511 76513 76518 76519 76520 76522 76525 76527 76528 76530 76531 76533 76534 76537 76538 76539 76540 76541 76542 76543 76544 76547 76548 76549 76550 76554 76556 76557 76559 76561 76565 76566 76567 76569 76571 76573 76574 76577 76578 76579 76649 76689 76690 76820 76824 76831 76832 76842 76844 76853 76856 76864 76869 76870 76871 76872 76877 76885 76890 77857 78605 78607 78608 78609 78611 78613 78615 78621 78626 78627 78628 78630 78633 78634 78639 78641 78642 78643 78646 78654 78657 78664 78665 78669 78672 78674 78680 78681 78683 78717 78728 78729 78750</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brazos Valley Community Action Programs</t>
   </si>
   <si>
@@ -257,34 +329,7 @@
     <t xml:space="preserve">Brazos; Burleson; Chambers; Grimes; Leon; Liberty; Madison; Montgomery; Robertson; Walker; Waller; Washington</t>
   </si>
   <si>
-    <t xml:space="preserve">Hill Country Community Action Association, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Saba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+13253725167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bell; Burnet; Coryell; Erath; Hamilton; Lampasas; Llano; Mason; Milam; Mills; San Saba; Somervell; Williamson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City of Austin Health and Human Services Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+15129725000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travis County Health &amp; Human Services/Veterans Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+15128547250</t>
+    <t xml:space="preserve">75831 75833 75846 75850 75852 75855 76629 76687 77301 77302 77303 77304 77305 77306 77316 77318 77320 77327 77328 77339 77340 77342 77353 77354 77355 77356 77357 77358 77362 77363 77365 77372 77378 77380 77381 77382 77384 77385 77386 77387 77393 77423 77426 77445 77446 77447 77484 77493 77514 77523 77533 77535 77538 77560 77564 77575 77580 77597 77665 77801 77802 77803 77805 77806 77807 77808 77830 77831 77833 77834 77835 77836 77837 77840 77841 77842 77845 77856 77859 77861 77864 77865 77868 77871 77872 77873 77879 77880 77881 78932 78946</t>
   </si>
   <si>
     <t xml:space="preserve">Community Council of South Central Texas, Inc.</t>
@@ -299,6 +344,24 @@
     <t xml:space="preserve">Atascosa; Bandera; Brewster; Comal; Crane; Culberson; Dimmit; Edwards; Frio; Gillespie; Guadalupe; Hudspeth; Jeff Davis; Karnes; Kendall; Kerr; Kinney; La Salle; Live Oak; Maverick; McMullen; Medina; Pecos; Presidio; Real; Terrell; Uvalde; Val Verde; Wilson; Zavala</t>
   </si>
   <si>
+    <t xml:space="preserve">78001 78003 78004 78005 78006 78007 78008 78009 78010 78011 78012 78013 78014 78015 78016 78017 78019 78021 78022 78024 78025 78026 78027 78028 78029 78039 78050 78052 78055 78056 78057 78058 78059 78060 78061 78062 78063 78064 78065 78066 78069 78070 78071 78072 78073 78074 78075 78101 78108 78111 78113 78114 78115 78116 78117 78118 78119 78121 78123 78124 78130 78131 78132 78133 78140 78141 78147 78151 78154 78155 78156 78160 78161 78163 78253 78264 78266 78350 78368 78383 78618 78623 78624 78631 78638 78648 78655 78670 78671 78675 78801 78802 78827 78828 78829 78830 78832 78833 78834 78836 78837 78838 78839 78840 78841 78842 78850 78851 78852 78853 78860 78861 78870 78871 78872 78873 78877 78879 78880 78881 78883 78884 78885 78886 79730 79731 79734 79735 79740 79743 79744 79781 79830 79837 79839 79842 79843 79845 79846 79847 79848 79851 79852 79854 79855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic Opportunities Advancement Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12547530331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosque; Ellis; Falls; Freestone; Hill; Johnson; Limestone; McLennan; Navarro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75102 75105 75109 75110 75119 75125 75144 75151 75152 75153 75154 75155 75165 75167 75168 75831 75838 75840 75846 75848 75855 75859 75860 76009 76028 76031 76033 76036 76041 76044 76050 76055 76058 76059 76061 76063 76064 76065 76084 76093 76097 76457 76524 76557 76570 76621 76622 76624 76626 76627 76628 76629 76630 76631 76632 76633 76634 76635 76636 76637 76638 76639 76640 76641 76642 76643 76645 76648 76649 76651 76652 76653 76655 76656 76657 76660 76661 76664 76665 76666 76667 76670 76671 76673 76676 76678 76679 76680 76681 76682 76685 76687 76689 76690 76691 76692 76693 76701 76702 76703 76704 76705 76706 76707 76708 76710 76711 76712 76714 76716 76798</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hidalgo County Community Services Agency</t>
   </si>
   <si>
@@ -311,16 +374,22 @@
     <t xml:space="preserve">Hidalgo</t>
   </si>
   <si>
-    <t xml:space="preserve">Economic Opportunities Advancement Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+12547530331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosque; Ellis; Falls; Freestone; Hill; Johnson; Limestone; McLennan; Navarro</t>
+    <t xml:space="preserve">78501 78502 78503 78504 78505 78516 78537 78538 78539 78540 78541 78542 78543 78557 78560 78562 78563 78570 78572 78573 78574 78576 78577 78579 78589 78595 78596 78599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling Plains Management Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crowell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+19406841571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archer; Baylor; Brown; Callahan; Clay; Comanche; Cottle; Eastland; Foard; Hardeman; Haskell; Hood; Jack; Jones; Kent; Knox; Montague; Palo Pinto; Parker; Shackelford; Stephens; Stonewall; Taylor; Throckmorton; Wichita; Wilbarger; Wise; Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76008 76020 76023 76035 76048 76049 76066 76067 76071 76073 76078 76082 76085 76086 76087 76088 76098 76108 76225 76228 76230 76234 76239 76251 76255 76261 76265 76270 76301 76302 76305 76306 76307 76308 76309 76310 76311 76351 76354 76357 76360 76363 76364 76365 76366 76367 76370 76371 76372 76373 76374 76377 76379 76380 76384 76388 76389 76424 76426 76427 76429 76430 76431 76432 76433 76435 76436 76437 76442 76443 76444 76445 76446 76448 76449 76450 76453 76454 76455 76458 76459 76460 76462 76463 76464 76468 76470 76471 76472 76474 76475 76476 76481 76483 76484 76486 76487 76490 76491 76801 76802 76803 76804 76823 76827 76857 76890 79225 79227 79247 79248 79252 79501 79502 79503 79504 79505 79508 79510 79518 79519 79520 79521 79525 79528 79529 79530 79533 79536 79539 79540 79541 79544 79547 79548 79553 79560 79561 79562 79563 79566 79601 79602 79603 79604 79605 79606 79607 79608</t>
   </si>
   <si>
     <t xml:space="preserve">El Paso Community Action, Project BRAVO</t>
@@ -332,16 +401,7 @@
     <t xml:space="preserve">+19155624100</t>
   </si>
   <si>
-    <t xml:space="preserve">Rolling Plains Management Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crowell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+19406841571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archer; Baylor; Brown; Callahan; Clay; Comanche; Cottle; Eastland; Foard; Hardeman; Haskell; Hood; Jack; Jones; Kent; Knox; Montague; Palo Pinto; Parker; Shackelford; Stephens; Stonewall; Taylor; Throckmorton; Wichita; Wilbarger; Wise; Young</t>
+    <t xml:space="preserve">79821 79835 79836 79838 79849 79853 79901 79902 79903 79904 79905 79906 79907 79908 79911 79912 79913 79914 79915 79916 79917 79922 79923 79924 79925 79926 79927 79928 79929 79930 79931 79932 79934 79935 79936 79937 79938 79940 79941 79942 79943 79944 79945 79946 79947 79948 79949 79950 79951 79952 79953 79954 79955 79995 79996 79997</t>
   </si>
   <si>
     <t xml:space="preserve">Williamson-Burnet County Opportunities, Inc.</t>
@@ -356,6 +416,9 @@
     <t xml:space="preserve">Burnet; Williamson</t>
   </si>
   <si>
+    <t xml:space="preserve">76511 76527 76530 76537 76550 76573 76574 76578 78605 78608 78611 78613 78615 78621 78626 78627 78628 78630 78633 78634 78639 78641 78642 78646 78654 78657 78664 78665 78669 78674 78680 78681 78683 78717 78728 78729 78750</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crossroads Community Action</t>
   </si>
   <si>
@@ -368,6 +431,9 @@
     <t xml:space="preserve">Aransas; Bee; Brazoria; Calhoun; DeWitt; Goliad; Gonzales; Jackson; Lavaca; Live Oak; Matagorda; McMullen; Refugio; Victoria; Wharton</t>
   </si>
   <si>
+    <t xml:space="preserve">77404 77414 77419 77420 77422 77428 77430 77434 77435 77437 77444 77448 77453 77454 77455 77457 77458 77465 77467 77468 77480 77482 77486 77488 77511 77512 77515 77516 77531 77534 77541 77542 77566 77577 77578 77581 77583 77584 77588 77901 77902 77903 77904 77905 77950 77951 77954 77957 77960 77961 77962 77963 77964 77967 77968 77969 77970 77971 77974 77975 77976 77977 77978 77979 77982 77983 77984 77986 77988 77990 77991 77994 77995 78007 78008 78022 78060 78071 78072 78075 78102 78104 78107 78119 78122 78125 78140 78141 78142 78146 78159 78162 78164 78336 78340 78350 78358 78368 78377 78381 78382 78383 78389 78391 78393 78614 78629 78632 78677 78956 78959</t>
+  </si>
+  <si>
     <t xml:space="preserve">Texas Neighborhood Services</t>
   </si>
   <si>
@@ -380,6 +446,9 @@
     <t xml:space="preserve">Erath; Hood; Johnson; Palo Pinto; Parker; Somervell; Wise</t>
   </si>
   <si>
+    <t xml:space="preserve">76008 76009 76020 76023 76028 76031 76033 76035 76036 76043 76044 76048 76049 76050 76058 76059 76061 76063 76066 76067 76070 76071 76073 76077 76078 76082 76084 76085 76086 76087 76088 76093 76097 76098 76108 76225 76234 76270 76401 76426 76429 76431 76433 76445 76446 76449 76453 76457 76462 76463 76465 76472 76475 76476 76484 76486 76487 76490 76649 76690</t>
+  </si>
+  <si>
     <t xml:space="preserve">West Texas Opportunities, Inc.</t>
   </si>
   <si>
@@ -392,6 +461,24 @@
     <t xml:space="preserve">Andrews; Borden; Dawson; Ector; Fisher; Gaines; Glasscock; Howard; Loving; Martin; Midland; Mitchell; Nolan; Reeves; Scurry; Upton; Ward; Winkler</t>
   </si>
   <si>
+    <t xml:space="preserve">79331 79342 79351 79359 79360 79377 79506 79511 79512 79517 79526 79527 79532 79534 79535 79537 79543 79545 79546 79549 79556 79560 79561 79565 79701 79702 79703 79704 79705 79706 79707 79708 79710 79712 79713 79714 79718 79719 79720 79733 79738 79739 79741 79742 79745 79748 79749 79752 79755 79756 79758 79759 79760 79761 79762 79763 79764 79765 79766 79768 79769 79770 79772 79777 79778 79782 79783 79785 79789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panhandle Community Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amarillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+18063722531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armstrong; Briscoe; Carson; Castro; Childress; Collingsworth; Dallam; Deaf Smith; Donley; Gray; Hall; Hansford; Hartley; Hemphill; Hutchinson; Lipscomb; Moore; Ochiltree; Oldham; Parmer; Potter; Randall; Roberts; Sherman; Swisher; Wheeler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73960 79001 79002 79003 79005 79007 79008 79009 79010 79011 79012 79013 79014 79015 79018 79019 79022 79024 79027 79029 79033 79034 79035 79036 79039 79040 79042 79043 79044 79045 79046 79051 79052 79056 79057 79058 79059 79061 79062 79063 79065 79066 79068 79070 79078 79079 79080 79081 79083 79084 79085 79086 79087 79088 79091 79092 79093 79094 79095 79096 79097 79098 79101 79102 79103 79104 79105 79106 79107 79108 79109 79110 79111 79114 79116 79117 79118 79119 79120 79121 79124 79159 79201 79226 79230 79237 79239 79240 79245 79251 79255 79257 79259 79261 79325 79347</t>
+  </si>
+  <si>
     <t xml:space="preserve">South Plains Community Action Association, Inc.</t>
   </si>
   <si>
@@ -404,16 +491,7 @@
     <t xml:space="preserve">Bailey; Cochran; Crosby; Dickens; Floyd; Garza; Hale; Hockley; King; Lamb; Lubbock; Lynn; Motley; Terry; Yoakum</t>
   </si>
   <si>
-    <t xml:space="preserve">Panhandle Community Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amarillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+18063722531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armstrong; Briscoe; Carson; Castro; Childress; Collingsworth; Dallam; Deaf Smith; Donley; Gray; Hall; Hansford; Hartley; Hemphill; Hutchinson; Lipscomb; Moore; Ochiltree; Oldham; Parmer; Potter; Randall; Roberts; Sherman; Swisher; Wheeler</t>
+    <t xml:space="preserve">79031 79032 79041 79043 79064 79072 79073 79082 79220 79221 79229 79234 79235 79236 79241 79243 79244 79248 79250 79255 79256 79258 79311 79312 79313 79314 79316 79322 79323 79324 79326 79329 79330 79336 79339 79343 79344 79345 79346 79347 79350 79351 79353 79355 79356 79357 79358 79359 79363 79364 79366 79367 79370 79371 79372 79373 79376 79381 79382 79401 79403 79404 79407 79408 79409 79410 79411 79412 79413 79414 79415 79416 79423 79424 79452 79453 79464 79490 79493 79499</t>
   </si>
   <si>
     <t xml:space="preserve">Southeast Texas Regional Planning Commission</t>
@@ -431,6 +509,54 @@
     <t xml:space="preserve">Hardin; Jefferson; Orange</t>
   </si>
   <si>
+    <t xml:space="preserve">77376 77519 77564 77585 77611 77613 77619 77622 77625 77627 77629 77630 77631 77632 77639 77640 77641 77642 77643 77651 77655 77656 77657 77659 77662 77663 77665 77670 77701 77702 77703 77704 77705 77706 77707 77708 77713 77720 77725 77726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueces County Community Action Agency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corpus Christi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+13618837201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78330 78339 78343 78351 78373 78380 78383 78401 78402 78403 78404 78405 78406 78407 78408 78409 78410 78411 78412 78413 78414 78415 78416 78417 78418 78419 78426 78427 78460 78463 78465 78466 78467 78468 78469 78480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tri-County Community Action, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+19365986315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison; Jasper; Newton; Panola; Sabine; San Augustine; Shelby; Tyler; Upshur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75601 75602 75605 75631 75633 75639 75640 75642 75643 75644 75645 75647 75650 75651 75661 75669 75670 75671 75672 75683 75686 75688 75691 75692 75755 75928 75929 75930 75931 75932 75933 75935 75936 75938 75942 75948 75951 75954 75956 75959 75966 75968 75972 75973 75974 75975 75977 75979 77612 77616 77624 77632 77660 77663 77664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community Services of Northeast Texas, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+19037565596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowie; Camp; Cass; Delta; Franklin; Hopkins; Lamar; Marion; Morris; Rains; Red River; Titus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75410 75411 75412 75415 75416 75417 75420 75421 75426 75431 75432 75433 75435 75436 75437 75440 75441 75446 75448 75450 75451 75453 75455 75456 75457 75460 75461 75462 75468 75469 75470 75471 75472 75473 75477 75478 75480 75481 75482 75483 75486 75487 75494 75497 75501 75503 75504 75505 75550 75551 75554 75555 75556 75558 75559 75560 75561 75562 75563 75564 75566 75567 75568 75569 75570 75571 75572 75574 75630 75638 75656 75657 75668 75683 75686</t>
+  </si>
+  <si>
     <t xml:space="preserve">Community Action Inc. of Central Texas</t>
   </si>
   <si>
@@ -443,16 +569,7 @@
     <t xml:space="preserve">Blanco; Caldwell; Hays</t>
   </si>
   <si>
-    <t xml:space="preserve">Nueces County Community Action Agency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corpus Christi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+13618837201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueces</t>
+    <t xml:space="preserve">78606 78610 78616 78619 78620 78632 78635 78636 78640 78644 78648 78652 78655 78656 78661 78662 78663 78666 78667 78676 78737 78953</t>
   </si>
   <si>
     <t xml:space="preserve">Guadalupe Economic Services Corporation</t>
@@ -467,24 +584,15 @@
     <t xml:space="preserve">WAP</t>
   </si>
   <si>
+    <t xml:space="preserve">79311 79329 79343 79350 79358 79363 79364 79366 79382 79401 79403 79404 79407 79408 79409 79410 79411 79412 79413 79414 79415 79416 79423 79424 79452 79453 79464 79490 79493 79499</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lubbock, City of, Community Development Department</t>
   </si>
   <si>
     <t xml:space="preserve">+18067752296</t>
   </si>
   <si>
-    <t xml:space="preserve">Community Services of Northeast Texas, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+19037565596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowie; Camp; Cass; Delta; Franklin; Hopkins; Lamar; Marion; Morris; Rains; Red River; Titus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Webb County Community Action Agency</t>
   </si>
   <si>
@@ -497,16 +605,7 @@
     <t xml:space="preserve">Webb</t>
   </si>
   <si>
-    <t xml:space="preserve">Tri-County Community Action, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+19365986315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison; Jasper; Newton; Panola; Sabine; San Augustine; Shelby; Tyler; Upshur</t>
+    <t xml:space="preserve">78019 78040 78041 78042 78043 78044 78045 78046 78344 78369 78371</t>
   </si>
   <si>
     <t xml:space="preserve">Concho Valley Community Action Agency</t>
@@ -521,6 +620,9 @@
     <t xml:space="preserve">Coke; Coleman; Concho; Crockett; Irion; Kimble; McCulloch; Menard; Reagan; Runnels; Schleicher; Sterling; Sutton; Tom Green</t>
   </si>
   <si>
+    <t xml:space="preserve">76821 76825 76828 76834 76836 76837 76841 76845 76848 76849 76852 76854 76858 76859 76861 76862 76865 76866 76871 76872 76873 76874 76875 76878 76882 76883 76884 76886 76887 76888 76901 76902 76903 76904 76905 76906 76908 76909 76930 76932 76933 76934 76935 76936 76937 76939 76940 76941 76943 76945 76950 76951 76955 76957 76958 79506 79519 79538 79566 79567 79739</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cornerstone Community Action Agency</t>
   </si>
   <si>
@@ -533,6 +635,9 @@
     <t xml:space="preserve">Brown; Callahan; Coleman; Comanche; Eastland; McCulloch; Runnels</t>
   </si>
   <si>
+    <t xml:space="preserve">76432 76435 76436 76437 76442 76443 76444 76445 76446 76448 76454 76455 76464 76468 76470 76471 76474 76801 76802 76803 76804 76821 76823 76825 76827 76828 76834 76836 76845 76852 76857 76858 76861 76865 76871 76872 76873 76875 76878 76882 76884 76887 76888 76890 76933 79504 79510 79519 79538 79566 79567</t>
+  </si>
+  <si>
     <t xml:space="preserve">South Texas Development Council</t>
   </si>
   <si>
@@ -542,6 +647,9 @@
     <t xml:space="preserve">Jim Hogg; Starr; Zapata</t>
   </si>
   <si>
+    <t xml:space="preserve">78067 78076 78360 78361 78536 78545 78547 78548 78564 78582 78584 78588 78591</t>
+  </si>
+  <si>
     <t xml:space="preserve">Economic Action Committee of the Gulf Coast</t>
   </si>
   <si>
@@ -554,6 +662,24 @@
     <t xml:space="preserve">Matagorda; Wharton</t>
   </si>
   <si>
+    <t xml:space="preserve">77404 77414 77419 77420 77428 77434 77435 77437 77448 77453 77454 77455 77457 77458 77465 77467 77468 77482 77488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspermont Small Business Development Center, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspermont</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+19409893538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haskell; Jones; Kent; Knox; Stonewall; Throckmorton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76363 76371 76372 76388 76483 76491 79227 79501 79502 79503 79505 79518 79520 79521 79525 79528 79529 79533 79536 79539 79540 79544 79547 79548 79553 79560 79561 79601</t>
+  </si>
+  <si>
     <t xml:space="preserve">Community Action Social Services &amp; Education</t>
   </si>
   <si>
@@ -566,16 +692,7 @@
     <t xml:space="preserve">Maverick</t>
   </si>
   <si>
-    <t xml:space="preserve">Aspermont Small Business Development Center, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aspermont</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+19409893538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haskell; Jones; Kent; Knox; Stonewall; Throckmorton</t>
+    <t xml:space="preserve">78852 78853 78860 78877</t>
   </si>
   <si>
     <t xml:space="preserve">Kleberg County Human Services</t>
@@ -590,6 +707,9 @@
     <t xml:space="preserve">Kenedy; Kleberg</t>
   </si>
   <si>
+    <t xml:space="preserve">78338 78363 78379 78385</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pecos County Community Action Agency</t>
   </si>
   <si>
@@ -602,6 +722,9 @@
     <t xml:space="preserve">Crane; Pecos; Terrell</t>
   </si>
   <si>
+    <t xml:space="preserve">78851 79730 79731 79735 79740 79743 79744 79781 79848</t>
+  </si>
+  <si>
     <t xml:space="preserve">How to use this sheet</t>
   </si>
   <si>
@@ -615,6 +738,12 @@
   </si>
   <si>
     <t xml:space="preserve">An organization runs several programs (CEAP, CSBG, WAP). One call covers all of them. The Programs column says which apply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counties vs ZIPs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counties are what the source declared. ZIP codes are the crosswalk expansion and are what the site actually searches on — HUD residential-share data, marginal slivers under 5% dropped. If an agency tells you their service area is different from what is listed, say so in Note; that correction is worth more than any other field on the row.</t>
   </si>
   <si>
     <t xml:space="preserve">Which cells to edit</t>
@@ -1399,7 +1528,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -1409,22 +1538,23 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="80"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1453,6 +1583,8 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -1466,11 +1598,11 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -1482,6 +1614,8 @@
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -1511,10 +1645,10 @@
       <c r="I3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="L3" s="5" t="s">
@@ -1552,6 +1686,12 @@
       </c>
       <c r="W3" s="5" t="s">
         <v>25</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1562,28 +1702,32 @@
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="9" t="n">
-        <v>5789933</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
+      <c r="H4" s="7" t="n">
+        <v>263</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>5745696</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
@@ -1596,6 +1740,8 @@
       <c r="U4" s="10"/>
       <c r="V4" s="10"/>
       <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
@@ -1605,28 +1751,32 @@
         <v>2</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>29</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="14" t="n">
-        <v>5789933</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="H5" s="12" t="n">
+        <v>263</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>5745696</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -1639,6 +1789,8 @@
       <c r="U5" s="10"/>
       <c r="V5" s="10"/>
       <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
@@ -1648,28 +1800,32 @@
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="9" t="n">
-        <v>3254583</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="H6" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>3013945</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
@@ -1682,6 +1838,8 @@
       <c r="U6" s="10"/>
       <c r="V6" s="10"/>
       <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
@@ -1691,28 +1849,32 @@
         <v>4</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H7" s="14" t="n">
-        <v>3107798</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="H7" s="12" t="n">
+        <v>198</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>2952503</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -1725,6 +1887,8 @@
       <c r="U7" s="10"/>
       <c r="V7" s="10"/>
       <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
@@ -1734,28 +1898,32 @@
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="G8" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>2879722</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2823843</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -1768,6 +1936,8 @@
       <c r="U8" s="10"/>
       <c r="V8" s="10"/>
       <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
@@ -1777,28 +1947,32 @@
         <v>6</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="14" t="n">
-        <v>2656028</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="H9" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>2823843</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
@@ -1811,6 +1985,8 @@
       <c r="U9" s="10"/>
       <c r="V9" s="10"/>
       <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
@@ -1820,28 +1996,32 @@
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>2656028</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+        <v>12</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>169</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>2679447</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
@@ -1854,6 +2034,8 @@
       <c r="U10" s="10"/>
       <c r="V10" s="10"/>
       <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15"/>
@@ -1861,28 +2043,32 @@
         <v>8</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H11" s="14" t="n">
-        <v>2398525</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+      <c r="H11" s="12" t="n">
+        <v>254</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>2411544</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
@@ -1895,6 +2081,8 @@
       <c r="U11" s="10"/>
       <c r="V11" s="10"/>
       <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
@@ -1904,28 +2092,32 @@
         <v>9</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="9" t="n">
-        <v>2230708</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="H12" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>2373979</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
@@ -1938,6 +2130,8 @@
       <c r="U12" s="10"/>
       <c r="V12" s="10"/>
       <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
@@ -1947,28 +2141,32 @@
         <v>10</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="14" t="n">
-        <v>2127737</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="H13" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>2107424</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>72</v>
+      </c>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
@@ -1981,6 +2179,8 @@
       <c r="U13" s="10"/>
       <c r="V13" s="10"/>
       <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
@@ -1990,28 +2190,32 @@
         <v>11</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="9" t="n">
-        <v>2127737</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="H14" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>2107424</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
@@ -2024,6 +2228,8 @@
       <c r="U14" s="10"/>
       <c r="V14" s="10"/>
       <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
@@ -2033,28 +2239,32 @@
         <v>12</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H15" s="14" t="n">
-        <v>1913209</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="H15" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>1859565</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
@@ -2067,6 +2277,8 @@
       <c r="U15" s="10"/>
       <c r="V15" s="10"/>
       <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
@@ -2076,28 +2288,32 @@
         <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="H16" s="9" t="n">
-        <v>1571177</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="H16" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>1670147</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
@@ -2110,35 +2326,43 @@
       <c r="U16" s="10"/>
       <c r="V16" s="10"/>
       <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15"/>
+      <c r="A17" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="B17" s="12" t="n">
         <v>14</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D17" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>1458960</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="I17" s="14" t="n">
+        <v>1642866</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>89</v>
+      </c>
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
@@ -2151,35 +2375,43 @@
       <c r="U17" s="10"/>
       <c r="V17" s="10"/>
       <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16"/>
+      <c r="A18" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="B18" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>1419307</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>1642866</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
@@ -2192,37 +2424,41 @@
       <c r="U18" s="10"/>
       <c r="V18" s="10"/>
       <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="A19" s="15"/>
       <c r="B19" s="12" t="n">
         <v>16</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>1363767</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>1373509</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>96</v>
+      </c>
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
@@ -2235,37 +2471,41 @@
       <c r="U19" s="10"/>
       <c r="V19" s="10"/>
       <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A20" s="16"/>
       <c r="B20" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>1363767</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
+        <v>12</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>1354836</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="L20" s="10"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
@@ -2278,6 +2518,8 @@
       <c r="U20" s="10"/>
       <c r="V20" s="10"/>
       <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15"/>
@@ -2285,28 +2527,32 @@
         <v>18</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H21" s="14" t="n">
-        <v>970756</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
+      <c r="H21" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>1022973</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
@@ -2319,37 +2565,41 @@
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A22" s="16"/>
       <c r="B22" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>914820</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>945408</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>111</v>
+      </c>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
@@ -2362,35 +2612,43 @@
       <c r="U22" s="10"/>
       <c r="V22" s="10"/>
       <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15"/>
+      <c r="A23" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="B23" s="12" t="n">
         <v>20</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>888575</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>869184</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>116</v>
+      </c>
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
@@ -2403,37 +2661,41 @@
       <c r="U23" s="10"/>
       <c r="V23" s="10"/>
       <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A24" s="16"/>
       <c r="B24" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>875784</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
+        <v>28</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>868903</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>121</v>
+      </c>
       <c r="L24" s="10"/>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
@@ -2446,35 +2708,43 @@
       <c r="U24" s="10"/>
       <c r="V24" s="10"/>
       <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15"/>
+      <c r="A25" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="B25" s="12" t="n">
         <v>22</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>861815</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>865537</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>125</v>
+      </c>
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
@@ -2487,6 +2757,8 @@
       <c r="U25" s="10"/>
       <c r="V25" s="10"/>
       <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16"/>
@@ -2494,28 +2766,32 @@
         <v>23</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>783202</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
+      <c r="H26" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>793830</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
@@ -2528,6 +2804,8 @@
       <c r="U26" s="10"/>
       <c r="V26" s="10"/>
       <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15"/>
@@ -2535,28 +2813,32 @@
         <v>24</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H27" s="14" t="n">
-        <v>763035</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
+      <c r="H27" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>770504</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>135</v>
+      </c>
       <c r="L27" s="10"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
@@ -2569,6 +2851,8 @@
       <c r="U27" s="10"/>
       <c r="V27" s="10"/>
       <c r="W27" s="10"/>
+      <c r="X27" s="10"/>
+      <c r="Y27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="16"/>
@@ -2576,28 +2860,32 @@
         <v>25</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H28" s="9" t="n">
-        <v>625480</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
+      <c r="H28" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>734252</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="L28" s="10"/>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
@@ -2610,6 +2898,8 @@
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
       <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15"/>
@@ -2617,28 +2907,32 @@
         <v>26</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H29" s="14" t="n">
-        <v>521481</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
+      <c r="H29" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>510349</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>145</v>
+      </c>
       <c r="L29" s="10"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -2651,6 +2945,8 @@
       <c r="U29" s="10"/>
       <c r="V29" s="10"/>
       <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16"/>
@@ -2658,28 +2954,32 @@
         <v>27</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>445960</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>439754</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="L30" s="10"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
@@ -2692,6 +2992,8 @@
       <c r="U30" s="10"/>
       <c r="V30" s="10"/>
       <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15"/>
@@ -2699,28 +3001,32 @@
         <v>28</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H31" s="14" t="n">
-        <v>438048</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>430794</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="L31" s="10"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
@@ -2733,6 +3039,8 @@
       <c r="U31" s="10"/>
       <c r="V31" s="10"/>
       <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="16"/>
@@ -2740,28 +3048,32 @@
         <v>29</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="9" t="n">
-        <v>398733</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
+      <c r="H32" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>408189</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>161</v>
+      </c>
       <c r="L32" s="10"/>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
@@ -2774,6 +3086,8 @@
       <c r="U32" s="10"/>
       <c r="V32" s="10"/>
       <c r="W32" s="10"/>
+      <c r="X32" s="10"/>
+      <c r="Y32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15"/>
@@ -2781,28 +3095,32 @@
         <v>30</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>357817</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>356424</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>166</v>
+      </c>
       <c r="L33" s="10"/>
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
@@ -2815,6 +3133,8 @@
       <c r="U33" s="10"/>
       <c r="V33" s="10"/>
       <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16"/>
@@ -2822,28 +3142,32 @@
         <v>31</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>353125</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>341265</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
@@ -2856,6 +3180,8 @@
       <c r="U34" s="10"/>
       <c r="V34" s="10"/>
       <c r="W34" s="10"/>
+      <c r="X34" s="10"/>
+      <c r="Y34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15"/>
@@ -2863,28 +3189,32 @@
         <v>32</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="14" t="n">
-        <v>327394</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
+        <v>12</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>339102</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>176</v>
+      </c>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
@@ -2897,6 +3227,8 @@
       <c r="U35" s="10"/>
       <c r="V35" s="10"/>
       <c r="W35" s="10"/>
+      <c r="X35" s="10"/>
+      <c r="Y35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16"/>
@@ -2904,28 +3236,32 @@
         <v>33</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>327394</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
+        <v>3</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>326428</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="L36" s="10"/>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
@@ -2938,6 +3274,8 @@
       <c r="U36" s="10"/>
       <c r="V36" s="10"/>
       <c r="W36" s="10"/>
+      <c r="X36" s="10"/>
+      <c r="Y36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15"/>
@@ -2945,28 +3283,32 @@
         <v>34</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H37" s="14" t="n">
-        <v>318807</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>309904</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>186</v>
+      </c>
       <c r="L37" s="10"/>
       <c r="M37" s="10"/>
       <c r="N37" s="10"/>
@@ -2979,6 +3321,8 @@
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
       <c r="W37" s="10"/>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="16"/>
@@ -2986,28 +3330,32 @@
         <v>35</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="9" t="n">
-        <v>272823</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
+      <c r="H38" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>309904</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>186</v>
+      </c>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
@@ -3020,6 +3368,8 @@
       <c r="U38" s="10"/>
       <c r="V38" s="10"/>
       <c r="W38" s="10"/>
+      <c r="X38" s="10"/>
+      <c r="Y38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15"/>
@@ -3027,28 +3377,32 @@
         <v>36</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <v>245834</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>268453</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>193</v>
+      </c>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
@@ -3061,6 +3415,8 @@
       <c r="U39" s="10"/>
       <c r="V39" s="10"/>
       <c r="W39" s="10"/>
+      <c r="X39" s="10"/>
+      <c r="Y39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="16"/>
@@ -3068,28 +3424,32 @@
         <v>37</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="H40" s="9" t="n">
-        <v>172748</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
+      <c r="H40" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>174876</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>198</v>
+      </c>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
@@ -3102,6 +3462,8 @@
       <c r="U40" s="10"/>
       <c r="V40" s="10"/>
       <c r="W40" s="10"/>
+      <c r="X40" s="10"/>
+      <c r="Y40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15"/>
@@ -3109,28 +3471,32 @@
         <v>38</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H41" s="14" t="n">
-        <v>111084</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
+      <c r="H41" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>119116</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>203</v>
+      </c>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -3143,6 +3509,8 @@
       <c r="U41" s="10"/>
       <c r="V41" s="10"/>
       <c r="W41" s="10"/>
+      <c r="X41" s="10"/>
+      <c r="Y41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="16"/>
@@ -3150,28 +3518,32 @@
         <v>39</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="9" t="n">
-        <v>84989</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
+      <c r="H42" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>84541</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>207</v>
+      </c>
       <c r="L42" s="10"/>
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
@@ -3184,6 +3556,8 @@
       <c r="U42" s="10"/>
       <c r="V42" s="10"/>
       <c r="W42" s="10"/>
+      <c r="X42" s="10"/>
+      <c r="Y42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15"/>
@@ -3191,28 +3565,32 @@
         <v>40</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H43" s="14" t="n">
-        <v>78426</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
+      <c r="H43" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>80918</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>212</v>
+      </c>
       <c r="L43" s="10"/>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
@@ -3225,6 +3603,8 @@
       <c r="U43" s="10"/>
       <c r="V43" s="10"/>
       <c r="W43" s="10"/>
+      <c r="X43" s="10"/>
+      <c r="Y43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="16"/>
@@ -3232,28 +3612,32 @@
         <v>41</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>58829</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>58752</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>217</v>
+      </c>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
       <c r="N44" s="10"/>
@@ -3266,6 +3650,8 @@
       <c r="U44" s="10"/>
       <c r="V44" s="10"/>
       <c r="W44" s="10"/>
+      <c r="X44" s="10"/>
+      <c r="Y44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15"/>
@@ -3273,28 +3659,32 @@
         <v>42</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H45" s="14" t="n">
-        <v>33010</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>57885</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="K45" s="13" t="s">
+        <v>222</v>
+      </c>
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
       <c r="N45" s="10"/>
@@ -3307,6 +3697,8 @@
       <c r="U45" s="10"/>
       <c r="V45" s="10"/>
       <c r="W45" s="10"/>
+      <c r="X45" s="10"/>
+      <c r="Y45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="16"/>
@@ -3314,28 +3706,32 @@
         <v>43</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H46" s="9" t="n">
-        <v>30772</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
+      <c r="H46" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" s="9" t="n">
+        <v>31324</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="L46" s="10"/>
       <c r="M46" s="10"/>
       <c r="N46" s="10"/>
@@ -3348,6 +3744,8 @@
       <c r="U46" s="10"/>
       <c r="V46" s="10"/>
       <c r="W46" s="10"/>
+      <c r="X46" s="10"/>
+      <c r="Y46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15"/>
@@ -3355,28 +3753,32 @@
         <v>44</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="14" t="n">
-        <v>20024</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
+      <c r="H47" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>20241</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="K47" s="13" t="s">
+        <v>232</v>
+      </c>
       <c r="L47" s="10"/>
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
@@ -3389,24 +3791,26 @@
       <c r="U47" s="10"/>
       <c r="V47" s="10"/>
       <c r="W47" s="10"/>
+      <c r="X47" s="10"/>
+      <c r="Y47" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:W47"/>
+  <autoFilter ref="A3:Y47"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="J2:W2"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="L2:Y2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Never a yes/no question. Ask: &quot;How far into the month is the funding usually lasting right now?&quot;" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="J4:J47" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Never a yes/no question. Ask: &quot;How far into the month is the funding usually lasting right now?&quot;" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="L4:L47" type="list">
       <formula1>"accepting,waitlist,funds_exhausted,seasonal_closed,appointment_only,unknown"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Read the prefilled fact back as a statement." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="M4:M47" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Read the prefilled fact back as a statement." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="O4:O47" type="list">
       <formula1>"walk_in,phone,online,appointment"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Log every attempt, including the ones that fail." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="T4:T47" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Log every attempt, including the ones that fail." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="V4:V47" type="list">
       <formula1>"reached,voicemail,no_answer,busy,wrong_number,callback_booked,refused,gatekeeper,disconnected"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3427,7 +3831,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3436,238 +3840,238 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="B1" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>206</v>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>226</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="19" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3675,64 +4079,72 @@
         <v>24</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>206</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="B39" s="24" t="str">
-        <f aca="false">COUNTA('Master List'!T4:T47)&amp;" of 44"</f>
-        <v>0 of 44</v>
+      <c r="A39" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B40" s="24" t="n">
-        <f aca="false">COUNTIF('Master List'!T4:T47,"reached")</f>
-        <v>0</v>
+        <v>283</v>
+      </c>
+      <c r="B40" s="24" t="str">
+        <f aca="false">COUNTA('Master List'!V4:V47)&amp;" of 44"</f>
+        <v>0 of 44</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="B41" s="24" t="n">
-        <f aca="false">COUNTIF('Master List'!J4:J47,"accepting")</f>
+        <f aca="false">COUNTIF('Master List'!V4:V47,"reached")</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B42" s="25" t="str">
-        <f aca="false">IFERROR(COUNTIF('Master List'!T4:T47,"reached")/COUNTA('Master List'!T4:T47),"—")</f>
+        <v>285</v>
+      </c>
+      <c r="B42" s="24" t="n">
+        <f aca="false">COUNTIF('Master List'!L4:L47,"accepting")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B43" s="25" t="str">
+        <f aca="false">IFERROR(COUNTIF('Master List'!V4:V47,"reached")/COUNTA('Master List'!V4:V47),"—")</f>
         <v>—</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="26" t="s">
-        <v>244</v>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="26" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/data/call-sheets/CornerHelp-Master-Provider-List.xlsx
+++ b/data/call-sheets/CornerHelp-Master-Provider-List.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Master List'!$A$3:$Y$47</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Master List'!$A$3:$AB$102</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,9 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="288">
-  <si>
-    <t xml:space="preserve">CornerHelp — master provider call sheet · 44 organizations · all 254 Texas counties</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="481">
+  <si>
+    <t xml:space="preserve">CornerHelp — master provider call sheet · 99 organizations · all 254 Texas counties</t>
   </si>
   <si>
     <t xml:space="preserve">DO NOT EDIT — call context</t>
@@ -47,12 +47,18 @@
     <t xml:space="preserve">City</t>
   </si>
   <si>
+    <t xml:space="preserve">Address</t>
+  </si>
+  <si>
     <t xml:space="preserve">Phone</t>
   </si>
   <si>
     <t xml:space="preserve">Programs</t>
   </si>
   <si>
+    <t xml:space="preserve">Help offered</t>
+  </si>
+  <si>
     <t xml:space="preserve">Counties</t>
   </si>
   <si>
@@ -68,6 +74,9 @@
     <t xml:space="preserve">ZIP codes served</t>
   </si>
   <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
@@ -122,18 +131,519 @@
     <t xml:space="preserve">CEAP, CSBG</t>
   </si>
   <si>
+    <t xml:space="preserve">electric_bill, food_pantry, gas_bill, reconnect_fee, rent_assistance, transportation, utility_deposit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brazoria; Galveston; Harris</t>
   </si>
   <si>
     <t xml:space="preserve">77001 77002 77003 77004 77005 77006 77007 77008 77009 77010 77011 77012 77013 77014 77015 77016 77017 77018 77019 77020 77021 77022 77023 77024 77025 77026 77027 77028 77029 77030 77031 77032 77033 77034 77035 77036 77037 77038 77039 77040 77041 77042 77043 77044 77045 77046 77047 77048 77049 77050 77051 77052 77053 77054 77055 77056 77057 77058 77059 77060 77061 77062 77063 77064 77065 77066 77067 77068 77069 77070 77071 77072 77073 77074 77075 77076 77077 77078 77079 77080 77081 77082 77083 77084 77085 77086 77087 77088 77089 77090 77091 77092 77093 77094 77095 77096 77098 77099 77205 77206 77207 77208 77210 77215 77217 77218 77219 77220 77221 77222 77223 77224 77225 77226 77227 77228 77230 77231 77233 77234 77235 77236 77237 77238 77240 77241 77242 77243 77244 77245 77248 77249 77251 77252 77253 77254 77255 77256 77257 77258 77259 77261 77262 77263 77265 77266 77267 77268 77269 77270 77271 77272 77273 77274 77275 77277 77279 77280 77282 77284 77287 77288 77289 77290 77291 77292 77293 77325 77336 77338 77339 77345 77346 77347 77373 77375 77377 77379 77383 77388 77389 77391 77396 77401 77402 77410 77411 77413 77422 77429 77430 77433 77444 77447 77449 77450 77477 77480 77484 77486 77491 77492 77493 77494 77501 77502 77503 77504 77505 77506 77507 77508 77510 77511 77512 77515 77516 77517 77518 77520 77521 77522 77523 77530 77531 77532 77534 77536 77539 77541 77542 77546 77547 77549 77550 77551 77552 77553 77554 77562 77563 77565 77566 77568 77571 77572 77573 77574 77577 77578 77581 77583 77584 77586 77587 77588 77590 77591 77592 77598 77617 77623 77650</t>
   </si>
   <si>
+    <t xml:space="preserve">TDHCA Master List of Community Affairs Subrecipients</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gulf Coast Community Services Association</t>
   </si>
   <si>
     <t xml:space="preserve">+17133934700</t>
   </si>
   <si>
+    <t xml:space="preserve">The Salvation Army — Northwest Community Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12507 Windfern Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistance services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Salvation Army Houston Area Command — Community Centers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Salvation Army — International Community Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7920 Cook Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Salvation Army — Aldine Westfield Community Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2600 Aldine Westfield Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Salvation Army — Temple Community Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4516 Irvington Blvd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Salvation Army — East Harris County Community Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasadena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2732 Cherry Brook Ln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities — Main Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2900 Louisiana Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17135264611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities Archdiocese of Galveston-Houston — Locations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities — Guadalupe Basic Needs Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326 South Jensen Drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities — St. Frances Cabrini Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5599 San Felipe Street, Suite 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17135954100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legal_aid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities — San Jose Clinic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2615 Fannin St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17138746590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">free_clinic, prescriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear Lake Food Pantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15700 Space Center Blvd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">food_pantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harris County Public Library — Food Banks and Food Assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klein United Methodist Church Food Pantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5290 FM 2920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17138593405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinity Klein Food Pantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5201 Spring Cypress Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12812904925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Hunger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMCA of Greater Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Society of St. Vincent de Paul of Harris County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17137418234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, food_pantry, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">needhelppayingbills.com — Harris County assistance programs (AGGREGATOR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southeast Area Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2102 Houston Blvd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17139440093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deposit_assistance, electric_bill, gas_vouchers, holiday_assistance, prescriptions, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wheeler Avenue Baptist Church Social Service Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3826 Wheeler Ave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17137485240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, food_pantry, mortgage_assistance, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. Joseph Social Ministry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4040 W Fuqua St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17132228903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, food_pantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. Mary Magdalene Social Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12815401907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. Justin Martyr Social Ministry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12815565116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, gas_bill, rent_assistance, water_bill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Community Service Center, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3434 Branard St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17138719741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dental, electric_bill, food_pantry, holiday_assistance, prescriptions, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cypress Assistance Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cypress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12930 Cypress North Houston Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12819557684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">holiday_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covenant House Texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1111 Lovett Blvd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17135232231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">free_clinic, holiday_assistance, prescriptions, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windsor Village United Methodist Church</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6011 W Orem Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17137238187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, food_pantry, mortgage_assistance, rent_assistance, transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memorial Assistance Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17134684516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, legal_aid, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northwest Assistance Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12818854555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deposit_assistance, food_pantry, gas_bill, hot_meals, mortgage_assistance, prescriptions, rent_assistance, transportation, water_bill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. Pius Catholic Church</t>
+  </si>
+  <si>
+    <t xml:space="preserve">824 Main St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17134739484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harris County Area Agency on Aging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8000 N Stadium Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+18323934301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">food_pantry, transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Brother's Keeper Outreach Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12621 Bissonnet St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12814989933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, food_pantry, holiday_assistance, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. John Vianney Social Ministry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">625 Nottingham Oaks Trail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12814971500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humble Area Assistance Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1302 First Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12814463663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deposit_assistance, electric_bill, eviction_prevention, legal_aid, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINC Houston Community Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800 Houston Ave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17134262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">food_pantry, gas_vouchers, prescriptions, rent_assistance, transportation, vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riceville Mt. Olive Baptist Church</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11539 S Gessner Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17137744880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">food_pantry, holiday_assistance, school_supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Houston Assistance Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17139779942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, food_pantry, holiday_assistance, mortgage_assistance, rent_assistance, transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interfaith Caring Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12813323881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katy Christian Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23232 Kingsland Blvd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12813915261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, holiday_assistance, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cathedral Health and Outreach Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1212 Prairie St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17132209737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dental, food_pantry, free_clinic, holiday_assistance, hot_meals, legal_aid, prescriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomball Emergency Assistance Ministries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 W Main St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12813516700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, gas_bill, prescriptions, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIDS Foundation Houston, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6260 Westpark Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17136236796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electric_bill, free_clinic, gas_vouchers, prescriptions, rent_assistance, transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bering Omega Community Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17135296071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">free_clinic, prescriptions, rent_assistance, transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brentwood Community Foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13033 1/2 Landmark Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17138522551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston Area Urban League</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17133938700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mortgage_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harris County Community Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9418 Jensen Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17136967900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">burial_assistance, electric_bill, food_pantry, rent_assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harris County Community Services — NW Satellite Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15555 Kuykendahl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star of Hope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wesley Community Center, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1410 Lee St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17132238131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaborative for Children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17136001100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">childcare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avance Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17138120033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harris County Department of Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17132733211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Way of Greater Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+17136852300</t>
+  </si>
+  <si>
     <t xml:space="preserve">Community Services, Inc.</t>
   </si>
   <si>
@@ -146,6 +656,9 @@
     <t xml:space="preserve">CEAP, WAP</t>
   </si>
   <si>
+    <t xml:space="preserve">electric_bill, gas_bill, home_repair, hvac_repair, reconnect_fee, utility_deposit, weatherization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anderson; Collin; Denton; Ellis; Henderson; Hunt; Kaufman; Navarro; Rockwall; Van Zandt</t>
   </si>
   <si>
@@ -164,6 +677,9 @@
     <t xml:space="preserve">CEAP, CSBG, WAP</t>
   </si>
   <si>
+    <t xml:space="preserve">electric_bill, food_pantry, gas_bill, home_repair, hvac_repair, reconnect_fee, rent_assistance, transportation, utility_deposit, weatherization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bowie; Camp; Cass; Collin; Cooke; Delta; Denton; Fannin; Franklin; Grayson; Hopkins; Hunt; Lamar; Marion; Morris; Rains; Red River; Rockwall; Titus</t>
   </si>
   <si>
@@ -347,6 +863,30 @@
     <t xml:space="preserve">78001 78003 78004 78005 78006 78007 78008 78009 78010 78011 78012 78013 78014 78015 78016 78017 78019 78021 78022 78024 78025 78026 78027 78028 78029 78039 78050 78052 78055 78056 78057 78058 78059 78060 78061 78062 78063 78064 78065 78066 78069 78070 78071 78072 78073 78074 78075 78101 78108 78111 78113 78114 78115 78116 78117 78118 78119 78121 78123 78124 78130 78131 78132 78133 78140 78141 78147 78151 78154 78155 78156 78160 78161 78163 78253 78264 78266 78350 78368 78383 78618 78623 78624 78631 78638 78648 78655 78670 78671 78675 78801 78802 78827 78828 78829 78830 78832 78833 78834 78836 78837 78838 78839 78840 78841 78842 78850 78851 78852 78853 78860 78861 78870 78871 78872 78873 78877 78879 78880 78881 78883 78884 78885 78886 79730 79731 79734 79735 79740 79743 79744 79781 79830 79837 79839 79842 79843 79845 79846 79847 79848 79851 79852 79854 79855</t>
   </si>
   <si>
+    <t xml:space="preserve">Catholic Charities — Mamie George Community Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1111 Collins Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12812026200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fort Bend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities — San Jose Clinic Rosenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1615 Avenue E</t>
+  </si>
+  <si>
     <t xml:space="preserve">Economic Opportunities Advancement Corporation</t>
   </si>
   <si>
@@ -434,6 +974,18 @@
     <t xml:space="preserve">77404 77414 77419 77420 77422 77428 77430 77434 77435 77437 77444 77448 77453 77454 77455 77457 77458 77465 77467 77468 77480 77482 77486 77488 77511 77512 77515 77516 77531 77534 77541 77542 77566 77577 77578 77581 77583 77584 77588 77901 77902 77903 77904 77905 77950 77951 77954 77957 77960 77961 77962 77963 77964 77967 77968 77969 77970 77971 77974 77975 77976 77977 77978 77979 77982 77983 77984 77986 77988 77990 77991 77994 77995 78007 78008 78022 78060 78071 78072 78075 78102 78104 78107 78119 78122 78125 78140 78141 78142 78146 78159 78162 78164 78336 78340 78350 78358 78368 78377 78381 78382 78383 78389 78391 78393 78614 78629 78632 78677 78956 78959</t>
   </si>
   <si>
+    <t xml:space="preserve">The Salvation Army — Conroe Community Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conroe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304 Avenue E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montgomery</t>
+  </si>
+  <si>
     <t xml:space="preserve">Texas Neighborhood Services</t>
   </si>
   <si>
@@ -506,12 +1058,36 @@
     <t xml:space="preserve">CEAP</t>
   </si>
   <si>
+    <t xml:space="preserve">electric_bill, gas_bill, reconnect_fee, utility_deposit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hardin; Jefferson; Orange</t>
   </si>
   <si>
     <t xml:space="preserve">77376 77519 77564 77585 77611 77613 77619 77622 77625 77627 77629 77630 77631 77632 77639 77640 77641 77642 77643 77651 77655 77656 77657 77659 77662 77663 77665 77670 77701 77702 77703 77704 77705 77706 77707 77708 77713 77720 77725 77726</t>
   </si>
   <si>
+    <t xml:space="preserve">Catholic Charities — Beacon of Hope Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galveston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4700 Broadway, Suite B-101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+14097622064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galveston County Food Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">624 4th Avenue N.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nueces County Community Action Agency</t>
   </si>
   <si>
@@ -582,6 +1158,9 @@
   </si>
   <si>
     <t xml:space="preserve">WAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_repair, hvac_repair, weatherization</t>
   </si>
   <si>
     <t xml:space="preserve">79311 79329 79343 79350 79358 79363 79364 79366 79382 79401 79403 79404 79407 79408 79409 79410 79411 79412 79413 79414 79415 79416 79423 79424 79452 79453 79464 79490 79493 79499</t>
@@ -1167,11 +1746,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1528,33 +2107,36 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:AB102"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1585,6 +2167,9 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -1600,12 +2185,12 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
@@ -1616,6 +2201,9 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -1651,13 +2239,13 @@
       <c r="K3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="O3" s="5" t="s">
@@ -1692,6 +2280,15 @@
       </c>
       <c r="Y3" s="5" t="s">
         <v>27</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1702,35 +2299,39 @@
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>30</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E4" s="8"/>
       <c r="F4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="J4" s="7" t="n">
         <v>263</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="K4" s="9" t="n">
         <v>5745696</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="L4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -1742,6 +2343,9 @@
       <c r="W4" s="10"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
@@ -1751,35 +2355,39 @@
         <v>2</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="12" t="n">
+      <c r="I5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="J5" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="K5" s="14" t="n">
         <v>5745696</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
+      <c r="L5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
@@ -1791,44 +2399,47 @@
       <c r="W5" s="10"/>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A6" s="15"/>
       <c r="B6" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>154</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>3013945</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
+        <v>32</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
@@ -1840,44 +2451,47 @@
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="10"/>
+      <c r="AB6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="A7" s="16"/>
       <c r="B7" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="H7" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="I7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>198</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>2952503</v>
-      </c>
-      <c r="J7" s="13" t="s">
+      <c r="M7" s="13"/>
+      <c r="N7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
@@ -1889,44 +2503,47 @@
       <c r="W7" s="10"/>
       <c r="X7" s="10"/>
       <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A8" s="15"/>
       <c r="B8" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>127</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>2823843</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
       <c r="Q8" s="10"/>
@@ -1938,44 +2555,47 @@
       <c r="W8" s="10"/>
       <c r="X8" s="10"/>
       <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10"/>
+      <c r="AB8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="A9" s="16"/>
       <c r="B9" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="12"/>
+      <c r="G9" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>2823843</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
@@ -1987,44 +2607,47 @@
       <c r="W9" s="10"/>
       <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="10"/>
+      <c r="AB9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A10" s="15"/>
       <c r="B10" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>169</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>2679447</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
       <c r="Q10" s="10"/>
@@ -2036,42 +2659,49 @@
       <c r="W10" s="10"/>
       <c r="X10" s="10"/>
       <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="12" t="n">
         <v>8</v>
       </c>
       <c r="C11" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>254</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>2411544</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
       <c r="Q11" s="10"/>
@@ -2083,44 +2713,49 @@
       <c r="W11" s="10"/>
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A12" s="15"/>
       <c r="B12" s="7" t="n">
         <v>9</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>66</v>
+        <v>32</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>2373979</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8" t="s">
+        <v>59</v>
+      </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
@@ -2132,44 +2767,49 @@
       <c r="W12" s="10"/>
       <c r="X12" s="10"/>
       <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="A13" s="16"/>
       <c r="B13" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>70</v>
+        <v>32</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="F13" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L13" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>2107424</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13" t="s">
+        <v>59</v>
+      </c>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
@@ -2181,44 +2821,49 @@
       <c r="W13" s="10"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A14" s="15"/>
       <c r="B14" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>74</v>
+        <v>32</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>2107424</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8" t="s">
+        <v>59</v>
+      </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
@@ -2230,44 +2875,47 @@
       <c r="W14" s="10"/>
       <c r="X14" s="10"/>
       <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="A15" s="16"/>
       <c r="B15" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L15" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>1859565</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
@@ -2279,44 +2927,49 @@
       <c r="W15" s="10"/>
       <c r="X15" s="10"/>
       <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A16" s="15"/>
       <c r="B16" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>82</v>
+        <v>75</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="F16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>1670147</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
@@ -2328,44 +2981,49 @@
       <c r="W16" s="10"/>
       <c r="X16" s="10"/>
       <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="A17" s="16"/>
       <c r="B17" s="12" t="n">
         <v>14</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>87</v>
+        <v>75</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="F17" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>1642866</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
@@ -2377,44 +3035,43 @@
       <c r="W17" s="10"/>
       <c r="X17" s="10"/>
       <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
+      <c r="AB17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A18" s="15"/>
       <c r="B18" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>1642866</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
@@ -2426,42 +3083,43 @@
       <c r="W18" s="10"/>
       <c r="X18" s="10"/>
       <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="12" t="n">
         <v>16</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L19" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>1373509</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
@@ -2473,42 +3131,45 @@
       <c r="W19" s="10"/>
       <c r="X19" s="10"/>
       <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>99</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>1354836</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
       <c r="Q20" s="10"/>
@@ -2520,42 +3181,49 @@
       <c r="W20" s="10"/>
       <c r="X20" s="10"/>
       <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="12" t="n">
         <v>18</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>104</v>
+        <v>88</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="F21" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L21" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>145</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>1022973</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
@@ -2567,42 +3235,49 @@
       <c r="W21" s="10"/>
       <c r="X21" s="10"/>
       <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>109</v>
+        <v>32</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="F22" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L22" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>945408</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="10"/>
@@ -2614,44 +3289,49 @@
       <c r="W22" s="10"/>
       <c r="X22" s="10"/>
       <c r="Y22" s="10"/>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10"/>
+      <c r="AB22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="A23" s="16"/>
       <c r="B23" s="12" t="n">
         <v>20</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>114</v>
+        <v>32</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="F23" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>869184</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O23" s="10"/>
       <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
@@ -2663,42 +3343,47 @@
       <c r="W23" s="10"/>
       <c r="X23" s="10"/>
       <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10"/>
+      <c r="AB23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>119</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="E24" s="8"/>
       <c r="F24" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>149</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>868903</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
@@ -2710,44 +3395,45 @@
       <c r="W24" s="10"/>
       <c r="X24" s="10"/>
       <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+      <c r="AA24" s="10"/>
+      <c r="AB24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="A25" s="16"/>
       <c r="B25" s="12" t="n">
         <v>22</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>124</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
       <c r="F25" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L25" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>865537</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
@@ -2759,42 +3445,49 @@
       <c r="W25" s="10"/>
       <c r="X25" s="10"/>
       <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
+      <c r="AA25" s="10"/>
+      <c r="AB25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>128</v>
+        <v>32</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>107</v>
       </c>
       <c r="F26" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>793830</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
       <c r="Q26" s="10"/>
@@ -2806,42 +3499,49 @@
       <c r="W26" s="10"/>
       <c r="X26" s="10"/>
       <c r="Y26" s="10"/>
+      <c r="Z26" s="10"/>
+      <c r="AA26" s="10"/>
+      <c r="AB26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15"/>
+      <c r="A27" s="16"/>
       <c r="B27" s="12" t="n">
         <v>24</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>133</v>
+        <v>111</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="F27" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>111</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>770504</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="10"/>
@@ -2853,42 +3553,49 @@
       <c r="W27" s="10"/>
       <c r="X27" s="10"/>
       <c r="Y27" s="10"/>
+      <c r="Z27" s="10"/>
+      <c r="AA27" s="10"/>
+      <c r="AB27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>138</v>
+        <v>32</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="F28" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L28" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>734252</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
       <c r="Q28" s="10"/>
@@ -2900,42 +3607,49 @@
       <c r="W28" s="10"/>
       <c r="X28" s="10"/>
       <c r="Y28" s="10"/>
+      <c r="Z28" s="10"/>
+      <c r="AA28" s="10"/>
+      <c r="AB28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="12" t="n">
         <v>26</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>143</v>
+        <v>32</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="F29" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L29" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>510349</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
@@ -2947,42 +3661,45 @@
       <c r="W29" s="10"/>
       <c r="X29" s="10"/>
       <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
+      <c r="AA29" s="10"/>
+      <c r="AB29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="7" t="n">
         <v>27</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>148</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="8"/>
       <c r="F30" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L30" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>439754</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O30" s="10"/>
       <c r="P30" s="10"/>
       <c r="Q30" s="10"/>
@@ -2994,42 +3711,45 @@
       <c r="W30" s="10"/>
       <c r="X30" s="10"/>
       <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
+      <c r="AA30" s="10"/>
+      <c r="AB30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="12" t="n">
         <v>28</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>153</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="13"/>
       <c r="F31" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L31" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>430794</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O31" s="10"/>
       <c r="P31" s="10"/>
       <c r="Q31" s="10"/>
@@ -3041,42 +3761,49 @@
       <c r="W31" s="10"/>
       <c r="X31" s="10"/>
       <c r="Y31" s="10"/>
+      <c r="Z31" s="10"/>
+      <c r="AA31" s="10"/>
+      <c r="AB31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="7" t="n">
         <v>29</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>158</v>
+        <v>54</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>408189</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
+        <v>131</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O32" s="10"/>
       <c r="P32" s="10"/>
       <c r="Q32" s="10"/>
@@ -3088,42 +3815,49 @@
       <c r="W32" s="10"/>
       <c r="X32" s="10"/>
       <c r="Y32" s="10"/>
+      <c r="Z32" s="10"/>
+      <c r="AA32" s="10"/>
+      <c r="AB32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15"/>
+      <c r="A33" s="16"/>
       <c r="B33" s="12" t="n">
         <v>30</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>164</v>
+        <v>32</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>133</v>
       </c>
       <c r="F33" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L33" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>356424</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O33" s="10"/>
       <c r="P33" s="10"/>
       <c r="Q33" s="10"/>
@@ -3135,42 +3869,49 @@
       <c r="W33" s="10"/>
       <c r="X33" s="10"/>
       <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+      <c r="AA33" s="10"/>
+      <c r="AB33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="7" t="n">
         <v>31</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>169</v>
+        <v>32</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="F34" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L34" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>341265</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
@@ -3182,42 +3923,49 @@
       <c r="W34" s="10"/>
       <c r="X34" s="10"/>
       <c r="Y34" s="10"/>
+      <c r="Z34" s="10"/>
+      <c r="AA34" s="10"/>
+      <c r="AB34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15"/>
+      <c r="A35" s="16"/>
       <c r="B35" s="12" t="n">
         <v>32</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>174</v>
+        <v>32</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="F35" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L35" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>339102</v>
-      </c>
-      <c r="J35" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O35" s="10"/>
       <c r="P35" s="10"/>
       <c r="Q35" s="10"/>
@@ -3229,42 +3977,49 @@
       <c r="W35" s="10"/>
       <c r="X35" s="10"/>
       <c r="Y35" s="10"/>
+      <c r="Z35" s="10"/>
+      <c r="AA35" s="10"/>
+      <c r="AB35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16"/>
+      <c r="A36" s="15"/>
       <c r="B36" s="7" t="n">
         <v>33</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>179</v>
+        <v>101</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="F36" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L36" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G36" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>326428</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O36" s="10"/>
       <c r="P36" s="10"/>
       <c r="Q36" s="10"/>
@@ -3276,42 +4031,49 @@
       <c r="W36" s="10"/>
       <c r="X36" s="10"/>
       <c r="Y36" s="10"/>
+      <c r="Z36" s="10"/>
+      <c r="AA36" s="10"/>
+      <c r="AB36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15"/>
+      <c r="A37" s="16"/>
       <c r="B37" s="12" t="n">
         <v>34</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>184</v>
+        <v>32</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>148</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="G37" s="12" t="n">
+        <v>149</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>309904</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
+      <c r="J37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
       <c r="Q37" s="10"/>
@@ -3323,42 +4085,49 @@
       <c r="W37" s="10"/>
       <c r="X37" s="10"/>
       <c r="Y37" s="10"/>
+      <c r="Z37" s="10"/>
+      <c r="AA37" s="10"/>
+      <c r="AB37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16"/>
+      <c r="A38" s="15"/>
       <c r="B38" s="7" t="n">
         <v>35</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>188</v>
+        <v>32</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G38" s="7" t="n">
+        <v>153</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I38" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>309904</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
+      <c r="J38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O38" s="10"/>
       <c r="P38" s="10"/>
       <c r="Q38" s="10"/>
@@ -3370,42 +4139,45 @@
       <c r="W38" s="10"/>
       <c r="X38" s="10"/>
       <c r="Y38" s="10"/>
+      <c r="Z38" s="10"/>
+      <c r="AA38" s="10"/>
+      <c r="AB38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15"/>
+      <c r="A39" s="16"/>
       <c r="B39" s="12" t="n">
         <v>36</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>191</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L39" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>268453</v>
-      </c>
-      <c r="J39" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="K39" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O39" s="10"/>
       <c r="P39" s="10"/>
       <c r="Q39" s="10"/>
@@ -3417,42 +4189,45 @@
       <c r="W39" s="10"/>
       <c r="X39" s="10"/>
       <c r="Y39" s="10"/>
+      <c r="Z39" s="10"/>
+      <c r="AA39" s="10"/>
+      <c r="AB39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="16"/>
+      <c r="A40" s="15"/>
       <c r="B40" s="7" t="n">
         <v>37</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>196</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c r="E40" s="8"/>
       <c r="F40" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L40" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G40" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>174876</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O40" s="10"/>
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
@@ -3464,42 +4239,49 @@
       <c r="W40" s="10"/>
       <c r="X40" s="10"/>
       <c r="Y40" s="10"/>
+      <c r="Z40" s="10"/>
+      <c r="AA40" s="10"/>
+      <c r="AB40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15"/>
+      <c r="A41" s="16"/>
       <c r="B41" s="12" t="n">
         <v>38</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>201</v>
+        <v>161</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="F41" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L41" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>119116</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O41" s="10"/>
       <c r="P41" s="10"/>
       <c r="Q41" s="10"/>
@@ -3511,42 +4293,49 @@
       <c r="W41" s="10"/>
       <c r="X41" s="10"/>
       <c r="Y41" s="10"/>
+      <c r="Z41" s="10"/>
+      <c r="AA41" s="10"/>
+      <c r="AB41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16"/>
+      <c r="A42" s="15"/>
       <c r="B42" s="7" t="n">
         <v>39</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>205</v>
+        <v>32</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>166</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>84541</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
+        <v>167</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
@@ -3558,42 +4347,49 @@
       <c r="W42" s="10"/>
       <c r="X42" s="10"/>
       <c r="Y42" s="10"/>
+      <c r="Z42" s="10"/>
+      <c r="AA42" s="10"/>
+      <c r="AB42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15"/>
+      <c r="A43" s="16"/>
       <c r="B43" s="12" t="n">
         <v>40</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>210</v>
+        <v>170</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>171</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>80918</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
+        <v>172</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O43" s="10"/>
       <c r="P43" s="10"/>
       <c r="Q43" s="10"/>
@@ -3605,42 +4401,49 @@
       <c r="W43" s="10"/>
       <c r="X43" s="10"/>
       <c r="Y43" s="10"/>
+      <c r="Z43" s="10"/>
+      <c r="AA43" s="10"/>
+      <c r="AB43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16"/>
+      <c r="A44" s="15"/>
       <c r="B44" s="7" t="n">
         <v>41</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>215</v>
+        <v>32</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="F44" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L44" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G44" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>58752</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O44" s="10"/>
       <c r="P44" s="10"/>
       <c r="Q44" s="10"/>
@@ -3652,42 +4455,45 @@
       <c r="W44" s="10"/>
       <c r="X44" s="10"/>
       <c r="Y44" s="10"/>
+      <c r="Z44" s="10"/>
+      <c r="AA44" s="10"/>
+      <c r="AB44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15"/>
+      <c r="A45" s="16"/>
       <c r="B45" s="12" t="n">
         <v>42</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>220</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="13"/>
       <c r="F45" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G45" s="12" t="n">
+        <v>179</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>57885</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="K45" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
+      <c r="J45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L45" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O45" s="10"/>
       <c r="P45" s="10"/>
       <c r="Q45" s="10"/>
@@ -3699,42 +4505,49 @@
       <c r="W45" s="10"/>
       <c r="X45" s="10"/>
       <c r="Y45" s="10"/>
+      <c r="Z45" s="10"/>
+      <c r="AA45" s="10"/>
+      <c r="AB45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16"/>
+      <c r="A46" s="15"/>
       <c r="B46" s="7" t="n">
         <v>43</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>225</v>
+        <v>32</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>182</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>31324</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
+        <v>183</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
       <c r="Q46" s="10"/>
@@ -3746,42 +4559,45 @@
       <c r="W46" s="10"/>
       <c r="X46" s="10"/>
       <c r="Y46" s="10"/>
+      <c r="Z46" s="10"/>
+      <c r="AA46" s="10"/>
+      <c r="AB46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15"/>
+      <c r="A47" s="16"/>
       <c r="B47" s="12" t="n">
         <v>44</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>230</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="D47" s="12"/>
+      <c r="E47" s="13"/>
       <c r="F47" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>20241</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="K47" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
+        <v>185</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L47" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="O47" s="10"/>
       <c r="P47" s="10"/>
       <c r="Q47" s="10"/>
@@ -3793,24 +4609,2999 @@
       <c r="W47" s="10"/>
       <c r="X47" s="10"/>
       <c r="Y47" s="10"/>
+      <c r="Z47" s="10"/>
+      <c r="AA47" s="10"/>
+      <c r="AB47" s="10"/>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15"/>
+      <c r="B48" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="10"/>
+      <c r="V48" s="10"/>
+      <c r="W48" s="10"/>
+      <c r="X48" s="10"/>
+      <c r="Y48" s="10"/>
+      <c r="Z48" s="10"/>
+      <c r="AA48" s="10"/>
+      <c r="AB48" s="10"/>
+    </row>
+    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="16"/>
+      <c r="B49" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L49" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
+      <c r="V49" s="10"/>
+      <c r="W49" s="10"/>
+      <c r="X49" s="10"/>
+      <c r="Y49" s="10"/>
+      <c r="Z49" s="10"/>
+      <c r="AA49" s="10"/>
+      <c r="AB49" s="10"/>
+    </row>
+    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15"/>
+      <c r="B50" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D50" s="7"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10"/>
+      <c r="U50" s="10"/>
+      <c r="V50" s="10"/>
+      <c r="W50" s="10"/>
+      <c r="X50" s="10"/>
+      <c r="Y50" s="10"/>
+      <c r="Z50" s="10"/>
+      <c r="AA50" s="10"/>
+      <c r="AB50" s="10"/>
+    </row>
+    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="16"/>
+      <c r="B51" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
+      <c r="V51" s="10"/>
+      <c r="W51" s="10"/>
+      <c r="X51" s="10"/>
+      <c r="Y51" s="10"/>
+      <c r="Z51" s="10"/>
+      <c r="AA51" s="10"/>
+      <c r="AB51" s="10"/>
+    </row>
+    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15"/>
+      <c r="B52" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D52" s="7"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="10"/>
+      <c r="V52" s="10"/>
+      <c r="W52" s="10"/>
+      <c r="X52" s="10"/>
+      <c r="Y52" s="10"/>
+      <c r="Z52" s="10"/>
+      <c r="AA52" s="10"/>
+      <c r="AB52" s="10"/>
+    </row>
+    <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="16"/>
+      <c r="B53" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D53" s="12"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L53" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Y53" s="10"/>
+      <c r="Z53" s="10"/>
+      <c r="AA53" s="10"/>
+      <c r="AB53" s="10"/>
+    </row>
+    <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15"/>
+      <c r="B54" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D54" s="7"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="10"/>
+      <c r="V54" s="10"/>
+      <c r="W54" s="10"/>
+      <c r="X54" s="10"/>
+      <c r="Y54" s="10"/>
+      <c r="Z54" s="10"/>
+      <c r="AA54" s="10"/>
+      <c r="AB54" s="10"/>
+    </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="16"/>
+      <c r="B55" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D55" s="12"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="14" t="n">
+        <v>5009302</v>
+      </c>
+      <c r="L55" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="10"/>
+      <c r="V55" s="10"/>
+      <c r="W55" s="10"/>
+      <c r="X55" s="10"/>
+      <c r="Y55" s="10"/>
+      <c r="Z55" s="10"/>
+      <c r="AA55" s="10"/>
+      <c r="AB55" s="10"/>
+    </row>
+    <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" s="8"/>
+      <c r="F56" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>3013945</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="N56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
+      <c r="V56" s="10"/>
+      <c r="W56" s="10"/>
+      <c r="X56" s="10"/>
+      <c r="Y56" s="10"/>
+      <c r="Z56" s="10"/>
+      <c r="AA56" s="10"/>
+      <c r="AB56" s="10"/>
+    </row>
+    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>198</v>
+      </c>
+      <c r="K57" s="14" t="n">
+        <v>2952503</v>
+      </c>
+      <c r="L57" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="M57" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="N57" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="10"/>
+      <c r="V57" s="10"/>
+      <c r="W57" s="10"/>
+      <c r="X57" s="10"/>
+      <c r="Y57" s="10"/>
+      <c r="Z57" s="10"/>
+      <c r="AA57" s="10"/>
+      <c r="AB57" s="10"/>
+    </row>
+    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E58" s="8"/>
+      <c r="F58" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>2823843</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="N58" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="10"/>
+      <c r="U58" s="10"/>
+      <c r="V58" s="10"/>
+      <c r="W58" s="10"/>
+      <c r="X58" s="10"/>
+      <c r="Y58" s="10"/>
+      <c r="Z58" s="10"/>
+      <c r="AA58" s="10"/>
+      <c r="AB58" s="10"/>
+    </row>
+    <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v>2823843</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="M59" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="N59" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
+      <c r="V59" s="10"/>
+      <c r="W59" s="10"/>
+      <c r="X59" s="10"/>
+      <c r="Y59" s="10"/>
+      <c r="Z59" s="10"/>
+      <c r="AA59" s="10"/>
+      <c r="AB59" s="10"/>
+    </row>
+    <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E60" s="8"/>
+      <c r="F60" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>169</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>2679447</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="10"/>
+      <c r="V60" s="10"/>
+      <c r="W60" s="10"/>
+      <c r="X60" s="10"/>
+      <c r="Y60" s="10"/>
+      <c r="Z60" s="10"/>
+      <c r="AA60" s="10"/>
+      <c r="AB60" s="10"/>
+    </row>
+    <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="16"/>
+      <c r="B61" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>254</v>
+      </c>
+      <c r="K61" s="14" t="n">
+        <v>2411544</v>
+      </c>
+      <c r="L61" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="M61" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="N61" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
+      <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
+      <c r="X61" s="10"/>
+      <c r="Y61" s="10"/>
+      <c r="Z61" s="10"/>
+      <c r="AA61" s="10"/>
+      <c r="AB61" s="10"/>
+    </row>
+    <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E62" s="8"/>
+      <c r="F62" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>2373979</v>
+      </c>
+      <c r="L62" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="N62" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="10"/>
+      <c r="X62" s="10"/>
+      <c r="Y62" s="10"/>
+      <c r="Z62" s="10"/>
+      <c r="AA62" s="10"/>
+      <c r="AB62" s="10"/>
+    </row>
+    <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v>2107424</v>
+      </c>
+      <c r="L63" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="M63" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="N63" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
+      <c r="V63" s="10"/>
+      <c r="W63" s="10"/>
+      <c r="X63" s="10"/>
+      <c r="Y63" s="10"/>
+      <c r="Z63" s="10"/>
+      <c r="AA63" s="10"/>
+      <c r="AB63" s="10"/>
+    </row>
+    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E64" s="8"/>
+      <c r="F64" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>2107424</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="N64" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
+      <c r="S64" s="10"/>
+      <c r="T64" s="10"/>
+      <c r="U64" s="10"/>
+      <c r="V64" s="10"/>
+      <c r="W64" s="10"/>
+      <c r="X64" s="10"/>
+      <c r="Y64" s="10"/>
+      <c r="Z64" s="10"/>
+      <c r="AA64" s="10"/>
+      <c r="AB64" s="10"/>
+    </row>
+    <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H65" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v>1859565</v>
+      </c>
+      <c r="L65" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="M65" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="N65" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
+      <c r="V65" s="10"/>
+      <c r="W65" s="10"/>
+      <c r="X65" s="10"/>
+      <c r="Y65" s="10"/>
+      <c r="Z65" s="10"/>
+      <c r="AA65" s="10"/>
+      <c r="AB65" s="10"/>
+    </row>
+    <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>1670147</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="M66" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="N66" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
+      <c r="S66" s="10"/>
+      <c r="T66" s="10"/>
+      <c r="U66" s="10"/>
+      <c r="V66" s="10"/>
+      <c r="W66" s="10"/>
+      <c r="X66" s="10"/>
+      <c r="Y66" s="10"/>
+      <c r="Z66" s="10"/>
+      <c r="AA66" s="10"/>
+      <c r="AB66" s="10"/>
+    </row>
+    <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="K67" s="14" t="n">
+        <v>1642866</v>
+      </c>
+      <c r="L67" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="M67" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="N67" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="10"/>
+      <c r="V67" s="10"/>
+      <c r="W67" s="10"/>
+      <c r="X67" s="10"/>
+      <c r="Y67" s="10"/>
+      <c r="Z67" s="10"/>
+      <c r="AA67" s="10"/>
+      <c r="AB67" s="10"/>
+    </row>
+    <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E68" s="8"/>
+      <c r="F68" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>1642866</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="N68" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="10"/>
+      <c r="V68" s="10"/>
+      <c r="W68" s="10"/>
+      <c r="X68" s="10"/>
+      <c r="Y68" s="10"/>
+      <c r="Z68" s="10"/>
+      <c r="AA68" s="10"/>
+      <c r="AB68" s="10"/>
+    </row>
+    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="16"/>
+      <c r="B69" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E69" s="13"/>
+      <c r="F69" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="K69" s="14" t="n">
+        <v>1373509</v>
+      </c>
+      <c r="L69" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="M69" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="N69" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
+      <c r="V69" s="10"/>
+      <c r="W69" s="10"/>
+      <c r="X69" s="10"/>
+      <c r="Y69" s="10"/>
+      <c r="Z69" s="10"/>
+      <c r="AA69" s="10"/>
+      <c r="AB69" s="10"/>
+    </row>
+    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="15"/>
+      <c r="B70" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E70" s="8"/>
+      <c r="F70" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>1354836</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M70" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="N70" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="10"/>
+      <c r="V70" s="10"/>
+      <c r="W70" s="10"/>
+      <c r="X70" s="10"/>
+      <c r="Y70" s="10"/>
+      <c r="Z70" s="10"/>
+      <c r="AA70" s="10"/>
+      <c r="AB70" s="10"/>
+    </row>
+    <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="16"/>
+      <c r="B71" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="K71" s="14" t="n">
+        <v>1022973</v>
+      </c>
+      <c r="L71" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="M71" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="N71" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
+      <c r="V71" s="10"/>
+      <c r="W71" s="10"/>
+      <c r="X71" s="10"/>
+      <c r="Y71" s="10"/>
+      <c r="Z71" s="10"/>
+      <c r="AA71" s="10"/>
+      <c r="AB71" s="10"/>
+    </row>
+    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="15"/>
+      <c r="B72" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>958434</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="M72" s="8"/>
+      <c r="N72" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="10"/>
+      <c r="U72" s="10"/>
+      <c r="V72" s="10"/>
+      <c r="W72" s="10"/>
+      <c r="X72" s="10"/>
+      <c r="Y72" s="10"/>
+      <c r="Z72" s="10"/>
+      <c r="AA72" s="10"/>
+      <c r="AB72" s="10"/>
+    </row>
+    <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="16"/>
+      <c r="B73" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="14" t="n">
+        <v>958434</v>
+      </c>
+      <c r="L73" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
+      <c r="V73" s="10"/>
+      <c r="W73" s="10"/>
+      <c r="X73" s="10"/>
+      <c r="Y73" s="10"/>
+      <c r="Z73" s="10"/>
+      <c r="AA73" s="10"/>
+      <c r="AB73" s="10"/>
+    </row>
+    <row r="74" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="15"/>
+      <c r="B74" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>945408</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="M74" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="N74" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
+      <c r="S74" s="10"/>
+      <c r="T74" s="10"/>
+      <c r="U74" s="10"/>
+      <c r="V74" s="10"/>
+      <c r="W74" s="10"/>
+      <c r="X74" s="10"/>
+      <c r="Y74" s="10"/>
+      <c r="Z74" s="10"/>
+      <c r="AA74" s="10"/>
+      <c r="AB74" s="10"/>
+    </row>
+    <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="E75" s="13"/>
+      <c r="F75" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K75" s="14" t="n">
+        <v>869184</v>
+      </c>
+      <c r="L75" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="M75" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="N75" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O75" s="10"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
+      <c r="V75" s="10"/>
+      <c r="W75" s="10"/>
+      <c r="X75" s="10"/>
+      <c r="Y75" s="10"/>
+      <c r="Z75" s="10"/>
+      <c r="AA75" s="10"/>
+      <c r="AB75" s="10"/>
+    </row>
+    <row r="76" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="15"/>
+      <c r="B76" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>868903</v>
+      </c>
+      <c r="L76" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="M76" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="N76" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O76" s="10"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
+      <c r="S76" s="10"/>
+      <c r="T76" s="10"/>
+      <c r="U76" s="10"/>
+      <c r="V76" s="10"/>
+      <c r="W76" s="10"/>
+      <c r="X76" s="10"/>
+      <c r="Y76" s="10"/>
+      <c r="Z76" s="10"/>
+      <c r="AA76" s="10"/>
+      <c r="AB76" s="10"/>
+    </row>
+    <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="E77" s="13"/>
+      <c r="F77" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K77" s="14" t="n">
+        <v>865537</v>
+      </c>
+      <c r="L77" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="M77" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="N77" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O77" s="10"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
+      <c r="V77" s="10"/>
+      <c r="W77" s="10"/>
+      <c r="X77" s="10"/>
+      <c r="Y77" s="10"/>
+      <c r="Z77" s="10"/>
+      <c r="AA77" s="10"/>
+      <c r="AB77" s="10"/>
+    </row>
+    <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="15"/>
+      <c r="B78" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E78" s="8"/>
+      <c r="F78" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>793830</v>
+      </c>
+      <c r="L78" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="M78" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="N78" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O78" s="10"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
+      <c r="S78" s="10"/>
+      <c r="T78" s="10"/>
+      <c r="U78" s="10"/>
+      <c r="V78" s="10"/>
+      <c r="W78" s="10"/>
+      <c r="X78" s="10"/>
+      <c r="Y78" s="10"/>
+      <c r="Z78" s="10"/>
+      <c r="AA78" s="10"/>
+      <c r="AB78" s="10"/>
+    </row>
+    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="16"/>
+      <c r="B79" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="E79" s="13"/>
+      <c r="F79" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J79" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="K79" s="14" t="n">
+        <v>770504</v>
+      </c>
+      <c r="L79" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="M79" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="N79" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O79" s="10"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="10"/>
+      <c r="V79" s="10"/>
+      <c r="W79" s="10"/>
+      <c r="X79" s="10"/>
+      <c r="Y79" s="10"/>
+      <c r="Z79" s="10"/>
+      <c r="AA79" s="10"/>
+      <c r="AB79" s="10"/>
+    </row>
+    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="15"/>
+      <c r="B80" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>749613</v>
+      </c>
+      <c r="L80" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="M80" s="8"/>
+      <c r="N80" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O80" s="10"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="10"/>
+      <c r="S80" s="10"/>
+      <c r="T80" s="10"/>
+      <c r="U80" s="10"/>
+      <c r="V80" s="10"/>
+      <c r="W80" s="10"/>
+      <c r="X80" s="10"/>
+      <c r="Y80" s="10"/>
+      <c r="Z80" s="10"/>
+      <c r="AA80" s="10"/>
+      <c r="AB80" s="10"/>
+    </row>
+    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="16"/>
+      <c r="B81" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="E81" s="13"/>
+      <c r="F81" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K81" s="14" t="n">
+        <v>734252</v>
+      </c>
+      <c r="L81" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="M81" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="N81" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O81" s="10"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
+      <c r="V81" s="10"/>
+      <c r="W81" s="10"/>
+      <c r="X81" s="10"/>
+      <c r="Y81" s="10"/>
+      <c r="Z81" s="10"/>
+      <c r="AA81" s="10"/>
+      <c r="AB81" s="10"/>
+    </row>
+    <row r="82" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="15"/>
+      <c r="B82" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E82" s="8"/>
+      <c r="F82" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>510349</v>
+      </c>
+      <c r="L82" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="M82" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="N82" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O82" s="10"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="10"/>
+      <c r="S82" s="10"/>
+      <c r="T82" s="10"/>
+      <c r="U82" s="10"/>
+      <c r="V82" s="10"/>
+      <c r="W82" s="10"/>
+      <c r="X82" s="10"/>
+      <c r="Y82" s="10"/>
+      <c r="Z82" s="10"/>
+      <c r="AA82" s="10"/>
+      <c r="AB82" s="10"/>
+    </row>
+    <row r="83" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="16"/>
+      <c r="B83" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E83" s="13"/>
+      <c r="F83" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J83" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="K83" s="14" t="n">
+        <v>439754</v>
+      </c>
+      <c r="L83" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="M83" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="N83" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O83" s="10"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="10"/>
+      <c r="U83" s="10"/>
+      <c r="V83" s="10"/>
+      <c r="W83" s="10"/>
+      <c r="X83" s="10"/>
+      <c r="Y83" s="10"/>
+      <c r="Z83" s="10"/>
+      <c r="AA83" s="10"/>
+      <c r="AB83" s="10"/>
+    </row>
+    <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="15"/>
+      <c r="B84" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E84" s="8"/>
+      <c r="F84" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J84" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>430794</v>
+      </c>
+      <c r="L84" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="M84" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="N84" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O84" s="10"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
+      <c r="S84" s="10"/>
+      <c r="T84" s="10"/>
+      <c r="U84" s="10"/>
+      <c r="V84" s="10"/>
+      <c r="W84" s="10"/>
+      <c r="X84" s="10"/>
+      <c r="Y84" s="10"/>
+      <c r="Z84" s="10"/>
+      <c r="AA84" s="10"/>
+      <c r="AB84" s="10"/>
+    </row>
+    <row r="85" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="16"/>
+      <c r="B85" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="E85" s="13"/>
+      <c r="F85" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K85" s="14" t="n">
+        <v>408189</v>
+      </c>
+      <c r="L85" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="M85" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="N85" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O85" s="10"/>
+      <c r="P85" s="10"/>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
+      <c r="U85" s="10"/>
+      <c r="V85" s="10"/>
+      <c r="W85" s="10"/>
+      <c r="X85" s="10"/>
+      <c r="Y85" s="10"/>
+      <c r="Z85" s="10"/>
+      <c r="AA85" s="10"/>
+      <c r="AB85" s="10"/>
+    </row>
+    <row r="86" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="15"/>
+      <c r="B86" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>367407</v>
+      </c>
+      <c r="L86" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="M86" s="8"/>
+      <c r="N86" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O86" s="10"/>
+      <c r="P86" s="10"/>
+      <c r="Q86" s="10"/>
+      <c r="R86" s="10"/>
+      <c r="S86" s="10"/>
+      <c r="T86" s="10"/>
+      <c r="U86" s="10"/>
+      <c r="V86" s="10"/>
+      <c r="W86" s="10"/>
+      <c r="X86" s="10"/>
+      <c r="Y86" s="10"/>
+      <c r="Z86" s="10"/>
+      <c r="AA86" s="10"/>
+      <c r="AB86" s="10"/>
+    </row>
+    <row r="87" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="16"/>
+      <c r="B87" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H87" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="14" t="n">
+        <v>367407</v>
+      </c>
+      <c r="L87" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="M87" s="13"/>
+      <c r="N87" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="O87" s="10"/>
+      <c r="P87" s="10"/>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="10"/>
+      <c r="U87" s="10"/>
+      <c r="V87" s="10"/>
+      <c r="W87" s="10"/>
+      <c r="X87" s="10"/>
+      <c r="Y87" s="10"/>
+      <c r="Z87" s="10"/>
+      <c r="AA87" s="10"/>
+      <c r="AB87" s="10"/>
+    </row>
+    <row r="88" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="15"/>
+      <c r="B88" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E88" s="8"/>
+      <c r="F88" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>356424</v>
+      </c>
+      <c r="L88" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="M88" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="N88" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O88" s="10"/>
+      <c r="P88" s="10"/>
+      <c r="Q88" s="10"/>
+      <c r="R88" s="10"/>
+      <c r="S88" s="10"/>
+      <c r="T88" s="10"/>
+      <c r="U88" s="10"/>
+      <c r="V88" s="10"/>
+      <c r="W88" s="10"/>
+      <c r="X88" s="10"/>
+      <c r="Y88" s="10"/>
+      <c r="Z88" s="10"/>
+      <c r="AA88" s="10"/>
+      <c r="AB88" s="10"/>
+    </row>
+    <row r="89" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="16"/>
+      <c r="B89" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="E89" s="13"/>
+      <c r="F89" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="G89" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I89" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K89" s="14" t="n">
+        <v>341265</v>
+      </c>
+      <c r="L89" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="M89" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="N89" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O89" s="10"/>
+      <c r="P89" s="10"/>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
+      <c r="V89" s="10"/>
+      <c r="W89" s="10"/>
+      <c r="X89" s="10"/>
+      <c r="Y89" s="10"/>
+      <c r="Z89" s="10"/>
+      <c r="AA89" s="10"/>
+      <c r="AB89" s="10"/>
+    </row>
+    <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="15"/>
+      <c r="B90" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E90" s="8"/>
+      <c r="F90" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I90" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J90" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>339102</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="M90" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="N90" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O90" s="10"/>
+      <c r="P90" s="10"/>
+      <c r="Q90" s="10"/>
+      <c r="R90" s="10"/>
+      <c r="S90" s="10"/>
+      <c r="T90" s="10"/>
+      <c r="U90" s="10"/>
+      <c r="V90" s="10"/>
+      <c r="W90" s="10"/>
+      <c r="X90" s="10"/>
+      <c r="Y90" s="10"/>
+      <c r="Z90" s="10"/>
+      <c r="AA90" s="10"/>
+      <c r="AB90" s="10"/>
+    </row>
+    <row r="91" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="16"/>
+      <c r="B91" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="E91" s="13"/>
+      <c r="F91" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K91" s="14" t="n">
+        <v>326428</v>
+      </c>
+      <c r="L91" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="M91" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="N91" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O91" s="10"/>
+      <c r="P91" s="10"/>
+      <c r="Q91" s="10"/>
+      <c r="R91" s="10"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="10"/>
+      <c r="U91" s="10"/>
+      <c r="V91" s="10"/>
+      <c r="W91" s="10"/>
+      <c r="X91" s="10"/>
+      <c r="Y91" s="10"/>
+      <c r="Z91" s="10"/>
+      <c r="AA91" s="10"/>
+      <c r="AB91" s="10"/>
+    </row>
+    <row r="92" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="15"/>
+      <c r="B92" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="E92" s="8"/>
+      <c r="F92" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="I92" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>309904</v>
+      </c>
+      <c r="L92" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="M92" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="N92" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O92" s="10"/>
+      <c r="P92" s="10"/>
+      <c r="Q92" s="10"/>
+      <c r="R92" s="10"/>
+      <c r="S92" s="10"/>
+      <c r="T92" s="10"/>
+      <c r="U92" s="10"/>
+      <c r="V92" s="10"/>
+      <c r="W92" s="10"/>
+      <c r="X92" s="10"/>
+      <c r="Y92" s="10"/>
+      <c r="Z92" s="10"/>
+      <c r="AA92" s="10"/>
+      <c r="AB92" s="10"/>
+    </row>
+    <row r="93" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="16"/>
+      <c r="B93" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="E93" s="13"/>
+      <c r="F93" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K93" s="14" t="n">
+        <v>309904</v>
+      </c>
+      <c r="L93" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="M93" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="N93" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O93" s="10"/>
+      <c r="P93" s="10"/>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
+      <c r="V93" s="10"/>
+      <c r="W93" s="10"/>
+      <c r="X93" s="10"/>
+      <c r="Y93" s="10"/>
+      <c r="Z93" s="10"/>
+      <c r="AA93" s="10"/>
+      <c r="AB93" s="10"/>
+    </row>
+    <row r="94" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="15"/>
+      <c r="B94" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="E94" s="8"/>
+      <c r="F94" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I94" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>268453</v>
+      </c>
+      <c r="L94" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="M94" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="N94" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O94" s="10"/>
+      <c r="P94" s="10"/>
+      <c r="Q94" s="10"/>
+      <c r="R94" s="10"/>
+      <c r="S94" s="10"/>
+      <c r="T94" s="10"/>
+      <c r="U94" s="10"/>
+      <c r="V94" s="10"/>
+      <c r="W94" s="10"/>
+      <c r="X94" s="10"/>
+      <c r="Y94" s="10"/>
+      <c r="Z94" s="10"/>
+      <c r="AA94" s="10"/>
+      <c r="AB94" s="10"/>
+    </row>
+    <row r="95" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="16"/>
+      <c r="B95" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="E95" s="13"/>
+      <c r="F95" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="K95" s="14" t="n">
+        <v>174876</v>
+      </c>
+      <c r="L95" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="M95" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="N95" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O95" s="10"/>
+      <c r="P95" s="10"/>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
+      <c r="V95" s="10"/>
+      <c r="W95" s="10"/>
+      <c r="X95" s="10"/>
+      <c r="Y95" s="10"/>
+      <c r="Z95" s="10"/>
+      <c r="AA95" s="10"/>
+      <c r="AB95" s="10"/>
+    </row>
+    <row r="96" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="15"/>
+      <c r="B96" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E96" s="8"/>
+      <c r="F96" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>119116</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="M96" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="N96" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O96" s="10"/>
+      <c r="P96" s="10"/>
+      <c r="Q96" s="10"/>
+      <c r="R96" s="10"/>
+      <c r="S96" s="10"/>
+      <c r="T96" s="10"/>
+      <c r="U96" s="10"/>
+      <c r="V96" s="10"/>
+      <c r="W96" s="10"/>
+      <c r="X96" s="10"/>
+      <c r="Y96" s="10"/>
+      <c r="Z96" s="10"/>
+      <c r="AA96" s="10"/>
+      <c r="AB96" s="10"/>
+    </row>
+    <row r="97" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="16"/>
+      <c r="B97" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="E97" s="13"/>
+      <c r="F97" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="G97" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K97" s="14" t="n">
+        <v>84541</v>
+      </c>
+      <c r="L97" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="M97" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="N97" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O97" s="10"/>
+      <c r="P97" s="10"/>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="10"/>
+      <c r="U97" s="10"/>
+      <c r="V97" s="10"/>
+      <c r="W97" s="10"/>
+      <c r="X97" s="10"/>
+      <c r="Y97" s="10"/>
+      <c r="Z97" s="10"/>
+      <c r="AA97" s="10"/>
+      <c r="AB97" s="10"/>
+    </row>
+    <row r="98" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="15"/>
+      <c r="B98" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E98" s="8"/>
+      <c r="F98" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="I98" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>80918</v>
+      </c>
+      <c r="L98" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="M98" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="N98" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O98" s="10"/>
+      <c r="P98" s="10"/>
+      <c r="Q98" s="10"/>
+      <c r="R98" s="10"/>
+      <c r="S98" s="10"/>
+      <c r="T98" s="10"/>
+      <c r="U98" s="10"/>
+      <c r="V98" s="10"/>
+      <c r="W98" s="10"/>
+      <c r="X98" s="10"/>
+      <c r="Y98" s="10"/>
+      <c r="Z98" s="10"/>
+      <c r="AA98" s="10"/>
+      <c r="AB98" s="10"/>
+    </row>
+    <row r="99" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="16"/>
+      <c r="B99" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="E99" s="13"/>
+      <c r="F99" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K99" s="14" t="n">
+        <v>58752</v>
+      </c>
+      <c r="L99" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="M99" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="N99" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O99" s="10"/>
+      <c r="P99" s="10"/>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
+      <c r="U99" s="10"/>
+      <c r="V99" s="10"/>
+      <c r="W99" s="10"/>
+      <c r="X99" s="10"/>
+      <c r="Y99" s="10"/>
+      <c r="Z99" s="10"/>
+      <c r="AA99" s="10"/>
+      <c r="AB99" s="10"/>
+    </row>
+    <row r="100" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="15"/>
+      <c r="B100" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E100" s="8"/>
+      <c r="F100" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="I100" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>57885</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="M100" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="N100" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O100" s="10"/>
+      <c r="P100" s="10"/>
+      <c r="Q100" s="10"/>
+      <c r="R100" s="10"/>
+      <c r="S100" s="10"/>
+      <c r="T100" s="10"/>
+      <c r="U100" s="10"/>
+      <c r="V100" s="10"/>
+      <c r="W100" s="10"/>
+      <c r="X100" s="10"/>
+      <c r="Y100" s="10"/>
+      <c r="Z100" s="10"/>
+      <c r="AA100" s="10"/>
+      <c r="AB100" s="10"/>
+    </row>
+    <row r="101" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="16"/>
+      <c r="B101" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="E101" s="13"/>
+      <c r="F101" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="H101" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" s="14" t="n">
+        <v>31324</v>
+      </c>
+      <c r="L101" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="M101" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="N101" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O101" s="10"/>
+      <c r="P101" s="10"/>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
+      <c r="U101" s="10"/>
+      <c r="V101" s="10"/>
+      <c r="W101" s="10"/>
+      <c r="X101" s="10"/>
+      <c r="Y101" s="10"/>
+      <c r="Z101" s="10"/>
+      <c r="AA101" s="10"/>
+      <c r="AB101" s="10"/>
+    </row>
+    <row r="102" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="15"/>
+      <c r="B102" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E102" s="8"/>
+      <c r="F102" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="I102" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>20241</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="M102" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="N102" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O102" s="10"/>
+      <c r="P102" s="10"/>
+      <c r="Q102" s="10"/>
+      <c r="R102" s="10"/>
+      <c r="S102" s="10"/>
+      <c r="T102" s="10"/>
+      <c r="U102" s="10"/>
+      <c r="V102" s="10"/>
+      <c r="W102" s="10"/>
+      <c r="X102" s="10"/>
+      <c r="Y102" s="10"/>
+      <c r="Z102" s="10"/>
+      <c r="AA102" s="10"/>
+      <c r="AB102" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Y47"/>
+  <autoFilter ref="A3:AB102"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:Y2"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="O2:AB2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Never a yes/no question. Ask: &quot;How far into the month is the funding usually lasting right now?&quot;" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="L4:L47" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Never a yes/no question. Ask: &quot;How far into the month is the funding usually lasting right now?&quot;" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="O4:O102" type="list">
       <formula1>"accepting,waitlist,funds_exhausted,seasonal_closed,appointment_only,unknown"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Read the prefilled fact back as a statement." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="O4:O47" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Read the prefilled fact back as a statement." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="R4:R102" type="list">
       <formula1>"walk_in,phone,online,appointment"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Log every attempt, including the ones that fail." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="V4:V47" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Log every attempt, including the ones that fail." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="Y4:Y102" type="list">
       <formula1>"reached,voicemail,no_answer,busy,wrong_number,callback_booked,refused,gatekeeper,disconnected"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3840,311 +7631,311 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>233</v>
+        <v>426</v>
       </c>
       <c r="B1" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>234</v>
+        <v>427</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>235</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>236</v>
+        <v>429</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>237</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>238</v>
+        <v>431</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>239</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>240</v>
+        <v>433</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>241</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>242</v>
+        <v>435</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>243</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>244</v>
+        <v>437</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>245</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>246</v>
+        <v>439</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>247</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>248</v>
+        <v>441</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>250</v>
+        <v>443</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>251</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>252</v>
+        <v>445</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>253</v>
+        <v>446</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>254</v>
+        <v>447</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>255</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>256</v>
+        <v>449</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>257</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>258</v>
+        <v>451</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>259</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>260</v>
+        <v>453</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>261</v>
+        <v>454</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>262</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>263</v>
+        <v>456</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>264</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>265</v>
+        <v>458</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>266</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>267</v>
+        <v>460</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18"/>
       <c r="B24" s="19" t="s">
-        <v>268</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>269</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>270</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>271</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>272</v>
+        <v>465</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>273</v>
+        <v>466</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>274</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>275</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>276</v>
+        <v>469</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>277</v>
+        <v>470</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>278</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>279</v>
+        <v>472</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>280</v>
+        <v>473</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>281</v>
+        <v>474</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>282</v>
+        <v>475</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>283</v>
+        <v>476</v>
       </c>
       <c r="B40" s="24" t="str">
-        <f aca="false">COUNTA('Master List'!V4:V47)&amp;" of 44"</f>
-        <v>0 of 44</v>
+        <f aca="false">COUNTA('Master List'!Y4:Y102)&amp;" of 99"</f>
+        <v>0 of 99</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>284</v>
+        <v>477</v>
       </c>
       <c r="B41" s="24" t="n">
-        <f aca="false">COUNTIF('Master List'!V4:V47,"reached")</f>
+        <f aca="false">COUNTIF('Master List'!Y4:Y102,"reached")</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>285</v>
+        <v>478</v>
       </c>
       <c r="B42" s="24" t="n">
-        <f aca="false">COUNTIF('Master List'!L4:L47,"accepting")</f>
+        <f aca="false">COUNTIF('Master List'!O4:O102,"accepting")</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>286</v>
+        <v>479</v>
       </c>
       <c r="B43" s="25" t="str">
-        <f aca="false">IFERROR(COUNTIF('Master List'!V4:V47,"reached")/COUNTA('Master List'!V4:V47),"—")</f>
+        <f aca="false">IFERROR(COUNTIF('Master List'!Y4:Y102,"reached")/COUNTA('Master List'!Y4:Y102),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="26" t="s">
-        <v>287</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/data/call-sheets/CornerHelp-Master-Provider-List.xlsx
+++ b/data/call-sheets/CornerHelp-Master-Provider-List.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Master List'!$A$3:$AB$102</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Master List'!$A$3:$AC$102</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="485">
   <si>
     <t xml:space="preserve">CornerHelp — master provider call sheet · 99 organizations · all 254 Texas counties</t>
   </si>
@@ -80,6 +80,9 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
+    <t xml:space="preserve">SERVICE AREA — which ZIPs?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Funding lasts until</t>
   </si>
   <si>
@@ -1331,6 +1334,12 @@
     <t xml:space="preserve">Only the YELLOW columns, from Status rightward. Navy columns are call context — leave them alone; they are how the row matches back to the database.</t>
   </si>
   <si>
+    <t xml:space="preserve">Service area is gating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A program does NOT publish on status alone. "Which ZIP codes do you actually cover?" is the second required question — the county list on this row is a crosswalk guess, and it is wrong: it gives every Harris agency 130 ZIPs when some serve five. Write what they say, verbatim, even if it is a neighbourhood name rather than ZIPs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blank beats guessed</t>
   </si>
   <si>
@@ -1434,6 +1443,9 @@
   </si>
   <si>
     <t xml:space="preserve">"People come in without the income for everybody in the house"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77042, 77057, 77063, 77077, 77082</t>
   </si>
   <si>
     <t xml:space="preserve">new intake system starting November</t>
@@ -2107,7 +2119,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB102"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2124,19 +2136,20 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2170,6 +2183,7 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -2204,6 +2218,7 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -2290,6 +2305,9 @@
       <c r="AB3" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="AC3" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
@@ -2299,20 +2317,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>3</v>
@@ -2324,13 +2342,13 @@
         <v>5745696</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
@@ -2346,6 +2364,7 @@
       <c r="Z4" s="10"/>
       <c r="AA4" s="10"/>
       <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
@@ -2355,20 +2374,20 @@
         <v>2</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I5" s="12" t="n">
         <v>3</v>
@@ -2380,13 +2399,13 @@
         <v>5745696</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
@@ -2402,6 +2421,7 @@
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
       <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15"/>
@@ -2409,20 +2429,20 @@
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>1</v>
@@ -2434,11 +2454,11 @@
         <v>5009302</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
@@ -2454,6 +2474,7 @@
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="10"/>
+      <c r="AC6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16"/>
@@ -2461,20 +2482,20 @@
         <v>4</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>1</v>
@@ -2486,11 +2507,11 @@
         <v>5009302</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
@@ -2506,6 +2527,7 @@
       <c r="Z7" s="10"/>
       <c r="AA7" s="10"/>
       <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15"/>
@@ -2513,20 +2535,20 @@
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>1</v>
@@ -2538,11 +2560,11 @@
         <v>5009302</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
@@ -2558,6 +2580,7 @@
       <c r="Z8" s="10"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="10"/>
+      <c r="AC8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16"/>
@@ -2565,20 +2588,20 @@
         <v>6</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>1</v>
@@ -2590,11 +2613,11 @@
         <v>5009302</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
@@ -2610,6 +2633,7 @@
       <c r="Z9" s="10"/>
       <c r="AA9" s="10"/>
       <c r="AB9" s="10"/>
+      <c r="AC9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15"/>
@@ -2617,20 +2641,20 @@
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>1</v>
@@ -2642,11 +2666,11 @@
         <v>5009302</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
@@ -2662,6 +2686,7 @@
       <c r="Z10" s="10"/>
       <c r="AA10" s="10"/>
       <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16"/>
@@ -2669,22 +2694,22 @@
         <v>8</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>1</v>
@@ -2696,11 +2721,11 @@
         <v>5009302</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
@@ -2716,6 +2741,7 @@
       <c r="Z11" s="10"/>
       <c r="AA11" s="10"/>
       <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15"/>
@@ -2723,22 +2749,22 @@
         <v>9</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>1</v>
@@ -2750,11 +2776,11 @@
         <v>5009302</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M12" s="8"/>
       <c r="N12" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
@@ -2770,6 +2796,7 @@
       <c r="Z12" s="10"/>
       <c r="AA12" s="10"/>
       <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16"/>
@@ -2777,22 +2804,22 @@
         <v>10</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>1</v>
@@ -2804,11 +2831,11 @@
         <v>5009302</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
@@ -2824,6 +2851,7 @@
       <c r="Z13" s="10"/>
       <c r="AA13" s="10"/>
       <c r="AB13" s="10"/>
+      <c r="AC13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15"/>
@@ -2831,22 +2859,22 @@
         <v>11</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>1</v>
@@ -2858,11 +2886,11 @@
         <v>5009302</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M14" s="8"/>
       <c r="N14" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
@@ -2878,6 +2906,7 @@
       <c r="Z14" s="10"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16"/>
@@ -2885,20 +2914,20 @@
         <v>12</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>1</v>
@@ -2910,11 +2939,11 @@
         <v>5009302</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
@@ -2930,6 +2959,7 @@
       <c r="Z15" s="10"/>
       <c r="AA15" s="10"/>
       <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15"/>
@@ -2937,22 +2967,22 @@
         <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>1</v>
@@ -2964,11 +2994,11 @@
         <v>5009302</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M16" s="8"/>
       <c r="N16" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
@@ -2984,6 +3014,7 @@
       <c r="Z16" s="10"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16"/>
@@ -2991,22 +3022,22 @@
         <v>14</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>1</v>
@@ -3018,11 +3049,11 @@
         <v>5009302</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
@@ -3038,6 +3069,7 @@
       <c r="Z17" s="10"/>
       <c r="AA17" s="10"/>
       <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15"/>
@@ -3045,16 +3077,16 @@
         <v>15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="8"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>1</v>
@@ -3066,11 +3098,11 @@
         <v>5009302</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
@@ -3086,6 +3118,7 @@
       <c r="Z18" s="10"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16"/>
@@ -3093,16 +3126,16 @@
         <v>16</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="13"/>
       <c r="F19" s="12"/>
       <c r="G19" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>1</v>
@@ -3114,11 +3147,11 @@
         <v>5009302</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
@@ -3134,6 +3167,7 @@
       <c r="Z19" s="10"/>
       <c r="AA19" s="10"/>
       <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15"/>
@@ -3141,18 +3175,18 @@
         <v>17</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="F20" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>1</v>
@@ -3164,11 +3198,11 @@
         <v>5009302</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M20" s="8"/>
       <c r="N20" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
@@ -3184,6 +3218,7 @@
       <c r="Z20" s="10"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16"/>
@@ -3191,22 +3226,22 @@
         <v>18</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>1</v>
@@ -3218,11 +3253,11 @@
         <v>5009302</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
@@ -3238,6 +3273,7 @@
       <c r="Z21" s="10"/>
       <c r="AA21" s="10"/>
       <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15"/>
@@ -3245,22 +3281,22 @@
         <v>19</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>1</v>
@@ -3272,11 +3308,11 @@
         <v>5009302</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M22" s="8"/>
       <c r="N22" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
@@ -3292,6 +3328,7 @@
       <c r="Z22" s="10"/>
       <c r="AA22" s="10"/>
       <c r="AB22" s="10"/>
+      <c r="AC22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16"/>
@@ -3299,22 +3336,22 @@
         <v>20</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>1</v>
@@ -3326,11 +3363,11 @@
         <v>5009302</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O23" s="10"/>
       <c r="P23" s="10"/>
@@ -3346,6 +3383,7 @@
       <c r="Z23" s="10"/>
       <c r="AA23" s="10"/>
       <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15"/>
@@ -3353,20 +3391,20 @@
         <v>21</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>1</v>
@@ -3378,11 +3416,11 @@
         <v>5009302</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M24" s="8"/>
       <c r="N24" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
@@ -3398,6 +3436,7 @@
       <c r="Z24" s="10"/>
       <c r="AA24" s="10"/>
       <c r="AB24" s="10"/>
+      <c r="AC24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16"/>
@@ -3405,18 +3444,18 @@
         <v>22</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="13"/>
       <c r="F25" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>1</v>
@@ -3428,11 +3467,11 @@
         <v>5009302</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M25" s="13"/>
       <c r="N25" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
@@ -3448,6 +3487,7 @@
       <c r="Z25" s="10"/>
       <c r="AA25" s="10"/>
       <c r="AB25" s="10"/>
+      <c r="AC25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15"/>
@@ -3455,22 +3495,22 @@
         <v>23</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>1</v>
@@ -3482,11 +3522,11 @@
         <v>5009302</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M26" s="8"/>
       <c r="N26" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
@@ -3502,6 +3542,7 @@
       <c r="Z26" s="10"/>
       <c r="AA26" s="10"/>
       <c r="AB26" s="10"/>
+      <c r="AC26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="16"/>
@@ -3509,22 +3550,22 @@
         <v>24</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>1</v>
@@ -3536,11 +3577,11 @@
         <v>5009302</v>
       </c>
       <c r="L27" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10"/>
@@ -3556,6 +3597,7 @@
       <c r="Z27" s="10"/>
       <c r="AA27" s="10"/>
       <c r="AB27" s="10"/>
+      <c r="AC27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15"/>
@@ -3563,22 +3605,22 @@
         <v>25</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>1</v>
@@ -3590,11 +3632,11 @@
         <v>5009302</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M28" s="8"/>
       <c r="N28" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
@@ -3610,6 +3652,7 @@
       <c r="Z28" s="10"/>
       <c r="AA28" s="10"/>
       <c r="AB28" s="10"/>
+      <c r="AC28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16"/>
@@ -3617,22 +3660,22 @@
         <v>26</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>1</v>
@@ -3644,11 +3687,11 @@
         <v>5009302</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
@@ -3664,6 +3707,7 @@
       <c r="Z29" s="10"/>
       <c r="AA29" s="10"/>
       <c r="AB29" s="10"/>
+      <c r="AC29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15"/>
@@ -3671,18 +3715,18 @@
         <v>27</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
       <c r="F30" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>1</v>
@@ -3694,11 +3738,11 @@
         <v>5009302</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M30" s="8"/>
       <c r="N30" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O30" s="10"/>
       <c r="P30" s="10"/>
@@ -3714,6 +3758,7 @@
       <c r="Z30" s="10"/>
       <c r="AA30" s="10"/>
       <c r="AB30" s="10"/>
+      <c r="AC30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="16"/>
@@ -3721,18 +3766,18 @@
         <v>28</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="13"/>
       <c r="F31" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>1</v>
@@ -3744,11 +3789,11 @@
         <v>5009302</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O31" s="10"/>
       <c r="P31" s="10"/>
@@ -3764,6 +3809,7 @@
       <c r="Z31" s="10"/>
       <c r="AA31" s="10"/>
       <c r="AB31" s="10"/>
+      <c r="AC31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15"/>
@@ -3771,22 +3817,22 @@
         <v>29</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>1</v>
@@ -3798,11 +3844,11 @@
         <v>5009302</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M32" s="8"/>
       <c r="N32" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O32" s="10"/>
       <c r="P32" s="10"/>
@@ -3818,6 +3864,7 @@
       <c r="Z32" s="10"/>
       <c r="AA32" s="10"/>
       <c r="AB32" s="10"/>
+      <c r="AC32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="16"/>
@@ -3825,22 +3872,22 @@
         <v>30</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>1</v>
@@ -3852,11 +3899,11 @@
         <v>5009302</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O33" s="10"/>
       <c r="P33" s="10"/>
@@ -3872,6 +3919,7 @@
       <c r="Z33" s="10"/>
       <c r="AA33" s="10"/>
       <c r="AB33" s="10"/>
+      <c r="AC33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15"/>
@@ -3879,22 +3927,22 @@
         <v>31</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>1</v>
@@ -3906,11 +3954,11 @@
         <v>5009302</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M34" s="8"/>
       <c r="N34" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
@@ -3926,6 +3974,7 @@
       <c r="Z34" s="10"/>
       <c r="AA34" s="10"/>
       <c r="AB34" s="10"/>
+      <c r="AC34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="16"/>
@@ -3933,22 +3982,22 @@
         <v>32</v>
       </c>
       <c r="C35" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>140</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>139</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>1</v>
@@ -3960,11 +4009,11 @@
         <v>5009302</v>
       </c>
       <c r="L35" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O35" s="10"/>
       <c r="P35" s="10"/>
@@ -3980,6 +4029,7 @@
       <c r="Z35" s="10"/>
       <c r="AA35" s="10"/>
       <c r="AB35" s="10"/>
+      <c r="AC35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15"/>
@@ -3987,22 +4037,22 @@
         <v>33</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>1</v>
@@ -4014,11 +4064,11 @@
         <v>5009302</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M36" s="8"/>
       <c r="N36" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O36" s="10"/>
       <c r="P36" s="10"/>
@@ -4034,6 +4084,7 @@
       <c r="Z36" s="10"/>
       <c r="AA36" s="10"/>
       <c r="AB36" s="10"/>
+      <c r="AC36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16"/>
@@ -4041,22 +4092,22 @@
         <v>34</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>1</v>
@@ -4068,11 +4119,11 @@
         <v>5009302</v>
       </c>
       <c r="L37" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
@@ -4088,6 +4139,7 @@
       <c r="Z37" s="10"/>
       <c r="AA37" s="10"/>
       <c r="AB37" s="10"/>
+      <c r="AC37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15"/>
@@ -4095,22 +4147,22 @@
         <v>35</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>1</v>
@@ -4122,11 +4174,11 @@
         <v>5009302</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M38" s="8"/>
       <c r="N38" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O38" s="10"/>
       <c r="P38" s="10"/>
@@ -4142,6 +4194,7 @@
       <c r="Z38" s="10"/>
       <c r="AA38" s="10"/>
       <c r="AB38" s="10"/>
+      <c r="AC38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="16"/>
@@ -4149,18 +4202,18 @@
         <v>36</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="13"/>
       <c r="F39" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>1</v>
@@ -4172,11 +4225,11 @@
         <v>5009302</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O39" s="10"/>
       <c r="P39" s="10"/>
@@ -4192,6 +4245,7 @@
       <c r="Z39" s="10"/>
       <c r="AA39" s="10"/>
       <c r="AB39" s="10"/>
+      <c r="AC39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15"/>
@@ -4199,18 +4253,18 @@
         <v>37</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I40" s="7" t="n">
         <v>1</v>
@@ -4222,11 +4276,11 @@
         <v>5009302</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M40" s="8"/>
       <c r="N40" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O40" s="10"/>
       <c r="P40" s="10"/>
@@ -4242,6 +4296,7 @@
       <c r="Z40" s="10"/>
       <c r="AA40" s="10"/>
       <c r="AB40" s="10"/>
+      <c r="AC40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="16"/>
@@ -4249,22 +4304,22 @@
         <v>38</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>1</v>
@@ -4276,11 +4331,11 @@
         <v>5009302</v>
       </c>
       <c r="L41" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O41" s="10"/>
       <c r="P41" s="10"/>
@@ -4296,6 +4351,7 @@
       <c r="Z41" s="10"/>
       <c r="AA41" s="10"/>
       <c r="AB41" s="10"/>
+      <c r="AC41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15"/>
@@ -4303,22 +4359,22 @@
         <v>39</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I42" s="7" t="n">
         <v>1</v>
@@ -4330,11 +4386,11 @@
         <v>5009302</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10"/>
@@ -4350,6 +4406,7 @@
       <c r="Z42" s="10"/>
       <c r="AA42" s="10"/>
       <c r="AB42" s="10"/>
+      <c r="AC42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="16"/>
@@ -4357,22 +4414,22 @@
         <v>40</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>1</v>
@@ -4384,11 +4441,11 @@
         <v>5009302</v>
       </c>
       <c r="L43" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O43" s="10"/>
       <c r="P43" s="10"/>
@@ -4404,6 +4461,7 @@
       <c r="Z43" s="10"/>
       <c r="AA43" s="10"/>
       <c r="AB43" s="10"/>
+      <c r="AC43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15"/>
@@ -4411,22 +4469,22 @@
         <v>41</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I44" s="7" t="n">
         <v>1</v>
@@ -4438,11 +4496,11 @@
         <v>5009302</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M44" s="8"/>
       <c r="N44" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O44" s="10"/>
       <c r="P44" s="10"/>
@@ -4458,6 +4516,7 @@
       <c r="Z44" s="10"/>
       <c r="AA44" s="10"/>
       <c r="AB44" s="10"/>
+      <c r="AC44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="16"/>
@@ -4465,18 +4524,18 @@
         <v>42</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="13"/>
       <c r="F45" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>1</v>
@@ -4488,11 +4547,11 @@
         <v>5009302</v>
       </c>
       <c r="L45" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M45" s="13"/>
       <c r="N45" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O45" s="10"/>
       <c r="P45" s="10"/>
@@ -4508,6 +4567,7 @@
       <c r="Z45" s="10"/>
       <c r="AA45" s="10"/>
       <c r="AB45" s="10"/>
+      <c r="AC45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15"/>
@@ -4515,22 +4575,22 @@
         <v>43</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I46" s="7" t="n">
         <v>1</v>
@@ -4542,11 +4602,11 @@
         <v>5009302</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M46" s="8"/>
       <c r="N46" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
@@ -4562,6 +4622,7 @@
       <c r="Z46" s="10"/>
       <c r="AA46" s="10"/>
       <c r="AB46" s="10"/>
+      <c r="AC46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="16"/>
@@ -4569,18 +4630,18 @@
         <v>44</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="13"/>
       <c r="F47" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>1</v>
@@ -4592,11 +4653,11 @@
         <v>5009302</v>
       </c>
       <c r="L47" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M47" s="13"/>
       <c r="N47" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O47" s="10"/>
       <c r="P47" s="10"/>
@@ -4612,6 +4673,7 @@
       <c r="Z47" s="10"/>
       <c r="AA47" s="10"/>
       <c r="AB47" s="10"/>
+      <c r="AC47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15"/>
@@ -4619,22 +4681,22 @@
         <v>45</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I48" s="7" t="n">
         <v>1</v>
@@ -4646,11 +4708,11 @@
         <v>5009302</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M48" s="8"/>
       <c r="N48" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O48" s="10"/>
       <c r="P48" s="10"/>
@@ -4666,6 +4728,7 @@
       <c r="Z48" s="10"/>
       <c r="AA48" s="10"/>
       <c r="AB48" s="10"/>
+      <c r="AC48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="16"/>
@@ -4673,22 +4736,22 @@
         <v>46</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>1</v>
@@ -4700,11 +4763,11 @@
         <v>5009302</v>
       </c>
       <c r="L49" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M49" s="13"/>
       <c r="N49" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O49" s="10"/>
       <c r="P49" s="10"/>
@@ -4720,6 +4783,7 @@
       <c r="Z49" s="10"/>
       <c r="AA49" s="10"/>
       <c r="AB49" s="10"/>
+      <c r="AC49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15"/>
@@ -4727,16 +4791,16 @@
         <v>47</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
       <c r="F50" s="7"/>
       <c r="G50" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I50" s="7" t="n">
         <v>1</v>
@@ -4748,11 +4812,11 @@
         <v>5009302</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M50" s="8"/>
       <c r="N50" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O50" s="10"/>
       <c r="P50" s="10"/>
@@ -4768,6 +4832,7 @@
       <c r="Z50" s="10"/>
       <c r="AA50" s="10"/>
       <c r="AB50" s="10"/>
+      <c r="AC50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="16"/>
@@ -4775,22 +4840,22 @@
         <v>48</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>1</v>
@@ -4802,11 +4867,11 @@
         <v>5009302</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M51" s="13"/>
       <c r="N51" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O51" s="10"/>
       <c r="P51" s="10"/>
@@ -4822,6 +4887,7 @@
       <c r="Z51" s="10"/>
       <c r="AA51" s="10"/>
       <c r="AB51" s="10"/>
+      <c r="AC51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15"/>
@@ -4829,18 +4895,18 @@
         <v>49</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
       <c r="F52" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I52" s="7" t="n">
         <v>1</v>
@@ -4852,11 +4918,11 @@
         <v>5009302</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M52" s="8"/>
       <c r="N52" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O52" s="10"/>
       <c r="P52" s="10"/>
@@ -4872,6 +4938,7 @@
       <c r="Z52" s="10"/>
       <c r="AA52" s="10"/>
       <c r="AB52" s="10"/>
+      <c r="AC52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="16"/>
@@ -4879,18 +4946,18 @@
         <v>50</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="13"/>
       <c r="F53" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>1</v>
@@ -4902,11 +4969,11 @@
         <v>5009302</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M53" s="13"/>
       <c r="N53" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O53" s="10"/>
       <c r="P53" s="10"/>
@@ -4922,6 +4989,7 @@
       <c r="Z53" s="10"/>
       <c r="AA53" s="10"/>
       <c r="AB53" s="10"/>
+      <c r="AC53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15"/>
@@ -4929,18 +4997,18 @@
         <v>51</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
       <c r="F54" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I54" s="7" t="n">
         <v>1</v>
@@ -4952,11 +5020,11 @@
         <v>5009302</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M54" s="8"/>
       <c r="N54" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O54" s="10"/>
       <c r="P54" s="10"/>
@@ -4972,6 +5040,7 @@
       <c r="Z54" s="10"/>
       <c r="AA54" s="10"/>
       <c r="AB54" s="10"/>
+      <c r="AC54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="16"/>
@@ -4979,18 +5048,18 @@
         <v>52</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="13"/>
       <c r="F55" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>1</v>
@@ -5002,11 +5071,11 @@
         <v>5009302</v>
       </c>
       <c r="L55" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M55" s="13"/>
       <c r="N55" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
@@ -5022,6 +5091,7 @@
       <c r="Z55" s="10"/>
       <c r="AA55" s="10"/>
       <c r="AB55" s="10"/>
+      <c r="AC55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
@@ -5031,20 +5101,20 @@
         <v>53</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I56" s="7" t="n">
         <v>10</v>
@@ -5056,13 +5126,13 @@
         <v>3013945</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N56" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
@@ -5078,6 +5148,7 @@
       <c r="Z56" s="10"/>
       <c r="AA56" s="10"/>
       <c r="AB56" s="10"/>
+      <c r="AC56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
@@ -5087,20 +5158,20 @@
         <v>54</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E57" s="13"/>
       <c r="F57" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>19</v>
@@ -5112,13 +5183,13 @@
         <v>2952503</v>
       </c>
       <c r="L57" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N57" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O57" s="10"/>
       <c r="P57" s="10"/>
@@ -5134,6 +5205,7 @@
       <c r="Z57" s="10"/>
       <c r="AA57" s="10"/>
       <c r="AB57" s="10"/>
+      <c r="AC57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
@@ -5143,20 +5215,20 @@
         <v>55</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I58" s="7" t="n">
         <v>1</v>
@@ -5168,13 +5240,13 @@
         <v>2823843</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N58" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O58" s="10"/>
       <c r="P58" s="10"/>
@@ -5190,6 +5262,7 @@
       <c r="Z58" s="10"/>
       <c r="AA58" s="10"/>
       <c r="AB58" s="10"/>
+      <c r="AC58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
@@ -5199,20 +5272,20 @@
         <v>56</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>1</v>
@@ -5224,13 +5297,13 @@
         <v>2823843</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N59" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
@@ -5246,6 +5319,7 @@
       <c r="Z59" s="10"/>
       <c r="AA59" s="10"/>
       <c r="AB59" s="10"/>
+      <c r="AC59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
@@ -5255,20 +5329,20 @@
         <v>57</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I60" s="7" t="n">
         <v>12</v>
@@ -5280,13 +5354,13 @@
         <v>2679447</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N60" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O60" s="10"/>
       <c r="P60" s="10"/>
@@ -5302,6 +5376,7 @@
       <c r="Z60" s="10"/>
       <c r="AA60" s="10"/>
       <c r="AB60" s="10"/>
+      <c r="AC60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="16"/>
@@ -5309,20 +5384,20 @@
         <v>58</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E61" s="13"/>
       <c r="F61" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>30</v>
@@ -5334,13 +5409,13 @@
         <v>2411544</v>
       </c>
       <c r="L61" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M61" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N61" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O61" s="10"/>
       <c r="P61" s="10"/>
@@ -5356,6 +5431,7 @@
       <c r="Z61" s="10"/>
       <c r="AA61" s="10"/>
       <c r="AB61" s="10"/>
+      <c r="AC61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
@@ -5365,20 +5441,20 @@
         <v>59</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E62" s="8"/>
       <c r="F62" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I62" s="7" t="n">
         <v>1</v>
@@ -5390,13 +5466,13 @@
         <v>2373979</v>
       </c>
       <c r="L62" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N62" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O62" s="10"/>
       <c r="P62" s="10"/>
@@ -5412,6 +5488,7 @@
       <c r="Z62" s="10"/>
       <c r="AA62" s="10"/>
       <c r="AB62" s="10"/>
+      <c r="AC62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
@@ -5421,20 +5498,20 @@
         <v>60</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>1</v>
@@ -5446,13 +5523,13 @@
         <v>2107424</v>
       </c>
       <c r="L63" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M63" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N63" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O63" s="10"/>
       <c r="P63" s="10"/>
@@ -5468,6 +5545,7 @@
       <c r="Z63" s="10"/>
       <c r="AA63" s="10"/>
       <c r="AB63" s="10"/>
+      <c r="AC63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
@@ -5477,20 +5555,20 @@
         <v>61</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I64" s="7" t="n">
         <v>1</v>
@@ -5502,13 +5580,13 @@
         <v>2107424</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M64" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N64" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
@@ -5524,6 +5602,7 @@
       <c r="Z64" s="10"/>
       <c r="AA64" s="10"/>
       <c r="AB64" s="10"/>
+      <c r="AC64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
@@ -5533,20 +5612,20 @@
         <v>62</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E65" s="13"/>
       <c r="F65" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>14</v>
@@ -5558,13 +5637,13 @@
         <v>1859565</v>
       </c>
       <c r="L65" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M65" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N65" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O65" s="10"/>
       <c r="P65" s="10"/>
@@ -5580,6 +5659,7 @@
       <c r="Z65" s="10"/>
       <c r="AA65" s="10"/>
       <c r="AB65" s="10"/>
+      <c r="AC65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
@@ -5589,20 +5669,20 @@
         <v>63</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I66" s="7" t="n">
         <v>10</v>
@@ -5614,13 +5694,13 @@
         <v>1670147</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M66" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N66" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O66" s="10"/>
       <c r="P66" s="10"/>
@@ -5636,6 +5716,7 @@
       <c r="Z66" s="10"/>
       <c r="AA66" s="10"/>
       <c r="AB66" s="10"/>
+      <c r="AC66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
@@ -5645,20 +5726,20 @@
         <v>64</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E67" s="13"/>
       <c r="F67" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>1</v>
@@ -5670,13 +5751,13 @@
         <v>1642866</v>
       </c>
       <c r="L67" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M67" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N67" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O67" s="10"/>
       <c r="P67" s="10"/>
@@ -5692,6 +5773,7 @@
       <c r="Z67" s="10"/>
       <c r="AA67" s="10"/>
       <c r="AB67" s="10"/>
+      <c r="AC67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
@@ -5701,20 +5783,20 @@
         <v>65</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I68" s="7" t="n">
         <v>1</v>
@@ -5726,13 +5808,13 @@
         <v>1642866</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M68" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N68" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O68" s="10"/>
       <c r="P68" s="10"/>
@@ -5748,6 +5830,7 @@
       <c r="Z68" s="10"/>
       <c r="AA68" s="10"/>
       <c r="AB68" s="10"/>
+      <c r="AC68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="16"/>
@@ -5755,20 +5838,20 @@
         <v>66</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>13</v>
@@ -5780,13 +5863,13 @@
         <v>1373509</v>
       </c>
       <c r="L69" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M69" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N69" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O69" s="10"/>
       <c r="P69" s="10"/>
@@ -5802,6 +5885,7 @@
       <c r="Z69" s="10"/>
       <c r="AA69" s="10"/>
       <c r="AB69" s="10"/>
+      <c r="AC69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="15"/>
@@ -5809,20 +5893,20 @@
         <v>67</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I70" s="7" t="n">
         <v>12</v>
@@ -5834,13 +5918,13 @@
         <v>1354836</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N70" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O70" s="10"/>
       <c r="P70" s="10"/>
@@ -5856,6 +5940,7 @@
       <c r="Z70" s="10"/>
       <c r="AA70" s="10"/>
       <c r="AB70" s="10"/>
+      <c r="AC70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="16"/>
@@ -5863,20 +5948,20 @@
         <v>68</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E71" s="13"/>
       <c r="F71" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>30</v>
@@ -5888,13 +5973,13 @@
         <v>1022973</v>
       </c>
       <c r="L71" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M71" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N71" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O71" s="10"/>
       <c r="P71" s="10"/>
@@ -5910,6 +5995,7 @@
       <c r="Z71" s="10"/>
       <c r="AA71" s="10"/>
       <c r="AB71" s="10"/>
+      <c r="AC71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="15"/>
@@ -5917,22 +6003,22 @@
         <v>69</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I72" s="7" t="n">
         <v>1</v>
@@ -5944,11 +6030,11 @@
         <v>958434</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M72" s="8"/>
       <c r="N72" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O72" s="10"/>
       <c r="P72" s="10"/>
@@ -5964,6 +6050,7 @@
       <c r="Z72" s="10"/>
       <c r="AA72" s="10"/>
       <c r="AB72" s="10"/>
+      <c r="AC72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="16"/>
@@ -5971,22 +6058,22 @@
         <v>70</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I73" s="12" t="n">
         <v>1</v>
@@ -5998,11 +6085,11 @@
         <v>958434</v>
       </c>
       <c r="L73" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M73" s="13"/>
       <c r="N73" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O73" s="10"/>
       <c r="P73" s="10"/>
@@ -6018,6 +6105,7 @@
       <c r="Z73" s="10"/>
       <c r="AA73" s="10"/>
       <c r="AB73" s="10"/>
+      <c r="AC73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="15"/>
@@ -6025,20 +6113,20 @@
         <v>71</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E74" s="8"/>
       <c r="F74" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I74" s="7" t="n">
         <v>9</v>
@@ -6050,13 +6138,13 @@
         <v>945408</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M74" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N74" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O74" s="10"/>
       <c r="P74" s="10"/>
@@ -6072,6 +6160,7 @@
       <c r="Z74" s="10"/>
       <c r="AA74" s="10"/>
       <c r="AB74" s="10"/>
+      <c r="AC74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="s">
@@ -6081,20 +6170,20 @@
         <v>72</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E75" s="13"/>
       <c r="F75" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>1</v>
@@ -6106,13 +6195,13 @@
         <v>869184</v>
       </c>
       <c r="L75" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M75" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N75" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O75" s="10"/>
       <c r="P75" s="10"/>
@@ -6128,6 +6217,7 @@
       <c r="Z75" s="10"/>
       <c r="AA75" s="10"/>
       <c r="AB75" s="10"/>
+      <c r="AC75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="15"/>
@@ -6135,20 +6225,20 @@
         <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I76" s="7" t="n">
         <v>28</v>
@@ -6160,13 +6250,13 @@
         <v>868903</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M76" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N76" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O76" s="10"/>
       <c r="P76" s="10"/>
@@ -6182,6 +6272,7 @@
       <c r="Z76" s="10"/>
       <c r="AA76" s="10"/>
       <c r="AB76" s="10"/>
+      <c r="AC76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
@@ -6191,20 +6282,20 @@
         <v>74</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E77" s="13"/>
       <c r="F77" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>1</v>
@@ -6216,13 +6307,13 @@
         <v>865537</v>
       </c>
       <c r="L77" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M77" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N77" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O77" s="10"/>
       <c r="P77" s="10"/>
@@ -6238,6 +6329,7 @@
       <c r="Z77" s="10"/>
       <c r="AA77" s="10"/>
       <c r="AB77" s="10"/>
+      <c r="AC77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="15"/>
@@ -6245,20 +6337,20 @@
         <v>75</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I78" s="7" t="n">
         <v>2</v>
@@ -6270,13 +6362,13 @@
         <v>793830</v>
       </c>
       <c r="L78" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M78" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N78" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O78" s="10"/>
       <c r="P78" s="10"/>
@@ -6292,6 +6384,7 @@
       <c r="Z78" s="10"/>
       <c r="AA78" s="10"/>
       <c r="AB78" s="10"/>
+      <c r="AC78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="16"/>
@@ -6299,20 +6392,20 @@
         <v>76</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E79" s="13"/>
       <c r="F79" s="12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I79" s="12" t="n">
         <v>15</v>
@@ -6324,13 +6417,13 @@
         <v>770504</v>
       </c>
       <c r="L79" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M79" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N79" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O79" s="10"/>
       <c r="P79" s="10"/>
@@ -6346,6 +6439,7 @@
       <c r="Z79" s="10"/>
       <c r="AA79" s="10"/>
       <c r="AB79" s="10"/>
+      <c r="AC79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="15"/>
@@ -6353,20 +6447,20 @@
         <v>77</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I80" s="7" t="n">
         <v>1</v>
@@ -6378,11 +6472,11 @@
         <v>749613</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M80" s="8"/>
       <c r="N80" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O80" s="10"/>
       <c r="P80" s="10"/>
@@ -6398,6 +6492,7 @@
       <c r="Z80" s="10"/>
       <c r="AA80" s="10"/>
       <c r="AB80" s="10"/>
+      <c r="AC80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="16"/>
@@ -6405,20 +6500,20 @@
         <v>78</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E81" s="13"/>
       <c r="F81" s="12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>7</v>
@@ -6430,13 +6525,13 @@
         <v>734252</v>
       </c>
       <c r="L81" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M81" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N81" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O81" s="10"/>
       <c r="P81" s="10"/>
@@ -6452,6 +6547,7 @@
       <c r="Z81" s="10"/>
       <c r="AA81" s="10"/>
       <c r="AB81" s="10"/>
+      <c r="AC81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="15"/>
@@ -6459,20 +6555,20 @@
         <v>79</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I82" s="7" t="n">
         <v>18</v>
@@ -6484,13 +6580,13 @@
         <v>510349</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M82" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N82" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O82" s="10"/>
       <c r="P82" s="10"/>
@@ -6506,6 +6602,7 @@
       <c r="Z82" s="10"/>
       <c r="AA82" s="10"/>
       <c r="AB82" s="10"/>
+      <c r="AC82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="16"/>
@@ -6513,20 +6610,20 @@
         <v>80</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E83" s="13"/>
       <c r="F83" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>26</v>
@@ -6538,13 +6635,13 @@
         <v>439754</v>
       </c>
       <c r="L83" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M83" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N83" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O83" s="10"/>
       <c r="P83" s="10"/>
@@ -6560,6 +6657,7 @@
       <c r="Z83" s="10"/>
       <c r="AA83" s="10"/>
       <c r="AB83" s="10"/>
+      <c r="AC83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="15"/>
@@ -6567,20 +6665,20 @@
         <v>81</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I84" s="7" t="n">
         <v>15</v>
@@ -6592,13 +6690,13 @@
         <v>430794</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M84" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N84" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O84" s="10"/>
       <c r="P84" s="10"/>
@@ -6614,6 +6712,7 @@
       <c r="Z84" s="10"/>
       <c r="AA84" s="10"/>
       <c r="AB84" s="10"/>
+      <c r="AC84" s="10"/>
     </row>
     <row r="85" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="16"/>
@@ -6621,20 +6720,20 @@
         <v>82</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E85" s="13"/>
       <c r="F85" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I85" s="12" t="n">
         <v>3</v>
@@ -6646,13 +6745,13 @@
         <v>408189</v>
       </c>
       <c r="L85" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M85" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N85" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O85" s="10"/>
       <c r="P85" s="10"/>
@@ -6668,6 +6767,7 @@
       <c r="Z85" s="10"/>
       <c r="AA85" s="10"/>
       <c r="AB85" s="10"/>
+      <c r="AC85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="15"/>
@@ -6675,22 +6775,22 @@
         <v>83</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I86" s="7" t="n">
         <v>1</v>
@@ -6702,11 +6802,11 @@
         <v>367407</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M86" s="8"/>
       <c r="N86" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O86" s="10"/>
       <c r="P86" s="10"/>
@@ -6722,6 +6822,7 @@
       <c r="Z86" s="10"/>
       <c r="AA86" s="10"/>
       <c r="AB86" s="10"/>
+      <c r="AC86" s="10"/>
     </row>
     <row r="87" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="16"/>
@@ -6729,20 +6830,20 @@
         <v>84</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F87" s="12"/>
       <c r="G87" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" s="12" t="n">
         <v>1</v>
@@ -6754,11 +6855,11 @@
         <v>367407</v>
       </c>
       <c r="L87" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M87" s="13"/>
       <c r="N87" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O87" s="10"/>
       <c r="P87" s="10"/>
@@ -6774,6 +6875,7 @@
       <c r="Z87" s="10"/>
       <c r="AA87" s="10"/>
       <c r="AB87" s="10"/>
+      <c r="AC87" s="10"/>
     </row>
     <row r="88" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="15"/>
@@ -6781,20 +6883,20 @@
         <v>85</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I88" s="7" t="n">
         <v>1</v>
@@ -6806,13 +6908,13 @@
         <v>356424</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M88" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N88" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O88" s="10"/>
       <c r="P88" s="10"/>
@@ -6828,6 +6930,7 @@
       <c r="Z88" s="10"/>
       <c r="AA88" s="10"/>
       <c r="AB88" s="10"/>
+      <c r="AC88" s="10"/>
     </row>
     <row r="89" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="16"/>
@@ -6835,20 +6938,20 @@
         <v>86</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E89" s="13"/>
       <c r="F89" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I89" s="12" t="n">
         <v>9</v>
@@ -6860,13 +6963,13 @@
         <v>341265</v>
       </c>
       <c r="L89" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M89" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N89" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O89" s="10"/>
       <c r="P89" s="10"/>
@@ -6882,6 +6985,7 @@
       <c r="Z89" s="10"/>
       <c r="AA89" s="10"/>
       <c r="AB89" s="10"/>
+      <c r="AC89" s="10"/>
     </row>
     <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="15"/>
@@ -6889,20 +6993,20 @@
         <v>87</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E90" s="8"/>
       <c r="F90" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I90" s="7" t="n">
         <v>12</v>
@@ -6914,13 +7018,13 @@
         <v>339102</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M90" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N90" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O90" s="10"/>
       <c r="P90" s="10"/>
@@ -6936,6 +7040,7 @@
       <c r="Z90" s="10"/>
       <c r="AA90" s="10"/>
       <c r="AB90" s="10"/>
+      <c r="AC90" s="10"/>
     </row>
     <row r="91" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="16"/>
@@ -6943,20 +7048,20 @@
         <v>88</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E91" s="13"/>
       <c r="F91" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I91" s="12" t="n">
         <v>3</v>
@@ -6968,13 +7073,13 @@
         <v>326428</v>
       </c>
       <c r="L91" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M91" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N91" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O91" s="10"/>
       <c r="P91" s="10"/>
@@ -6990,6 +7095,7 @@
       <c r="Z91" s="10"/>
       <c r="AA91" s="10"/>
       <c r="AB91" s="10"/>
+      <c r="AC91" s="10"/>
     </row>
     <row r="92" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="15"/>
@@ -6997,20 +7103,20 @@
         <v>89</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I92" s="7" t="n">
         <v>1</v>
@@ -7022,13 +7128,13 @@
         <v>309904</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M92" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N92" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O92" s="10"/>
       <c r="P92" s="10"/>
@@ -7044,6 +7150,7 @@
       <c r="Z92" s="10"/>
       <c r="AA92" s="10"/>
       <c r="AB92" s="10"/>
+      <c r="AC92" s="10"/>
     </row>
     <row r="93" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="16"/>
@@ -7051,20 +7158,20 @@
         <v>90</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E93" s="13"/>
       <c r="F93" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I93" s="12" t="n">
         <v>1</v>
@@ -7076,13 +7183,13 @@
         <v>309904</v>
       </c>
       <c r="L93" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M93" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N93" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O93" s="10"/>
       <c r="P93" s="10"/>
@@ -7098,6 +7205,7 @@
       <c r="Z93" s="10"/>
       <c r="AA93" s="10"/>
       <c r="AB93" s="10"/>
+      <c r="AC93" s="10"/>
     </row>
     <row r="94" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="15"/>
@@ -7105,20 +7213,20 @@
         <v>91</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E94" s="8"/>
       <c r="F94" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I94" s="7" t="n">
         <v>1</v>
@@ -7130,13 +7238,13 @@
         <v>268453</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M94" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N94" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O94" s="10"/>
       <c r="P94" s="10"/>
@@ -7152,6 +7260,7 @@
       <c r="Z94" s="10"/>
       <c r="AA94" s="10"/>
       <c r="AB94" s="10"/>
+      <c r="AC94" s="10"/>
     </row>
     <row r="95" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="16"/>
@@ -7159,20 +7268,20 @@
         <v>92</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E95" s="13"/>
       <c r="F95" s="12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I95" s="12" t="n">
         <v>14</v>
@@ -7184,13 +7293,13 @@
         <v>174876</v>
       </c>
       <c r="L95" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M95" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N95" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O95" s="10"/>
       <c r="P95" s="10"/>
@@ -7206,6 +7315,7 @@
       <c r="Z95" s="10"/>
       <c r="AA95" s="10"/>
       <c r="AB95" s="10"/>
+      <c r="AC95" s="10"/>
     </row>
     <row r="96" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="15"/>
@@ -7213,20 +7323,20 @@
         <v>93</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E96" s="8"/>
       <c r="F96" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I96" s="7" t="n">
         <v>7</v>
@@ -7238,13 +7348,13 @@
         <v>119116</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O96" s="10"/>
       <c r="P96" s="10"/>
@@ -7260,6 +7370,7 @@
       <c r="Z96" s="10"/>
       <c r="AA96" s="10"/>
       <c r="AB96" s="10"/>
+      <c r="AC96" s="10"/>
     </row>
     <row r="97" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="16"/>
@@ -7267,20 +7378,20 @@
         <v>94</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E97" s="13"/>
       <c r="F97" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I97" s="12" t="n">
         <v>3</v>
@@ -7292,13 +7403,13 @@
         <v>84541</v>
       </c>
       <c r="L97" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M97" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N97" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O97" s="10"/>
       <c r="P97" s="10"/>
@@ -7314,6 +7425,7 @@
       <c r="Z97" s="10"/>
       <c r="AA97" s="10"/>
       <c r="AB97" s="10"/>
+      <c r="AC97" s="10"/>
     </row>
     <row r="98" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="15"/>
@@ -7321,20 +7433,20 @@
         <v>95</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I98" s="7" t="n">
         <v>2</v>
@@ -7346,13 +7458,13 @@
         <v>80918</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M98" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N98" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O98" s="10"/>
       <c r="P98" s="10"/>
@@ -7368,6 +7480,7 @@
       <c r="Z98" s="10"/>
       <c r="AA98" s="10"/>
       <c r="AB98" s="10"/>
+      <c r="AC98" s="10"/>
     </row>
     <row r="99" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="16"/>
@@ -7375,20 +7488,20 @@
         <v>96</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E99" s="13"/>
       <c r="F99" s="12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I99" s="12" t="n">
         <v>6</v>
@@ -7400,13 +7513,13 @@
         <v>58752</v>
       </c>
       <c r="L99" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M99" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N99" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O99" s="10"/>
       <c r="P99" s="10"/>
@@ -7422,6 +7535,7 @@
       <c r="Z99" s="10"/>
       <c r="AA99" s="10"/>
       <c r="AB99" s="10"/>
+      <c r="AC99" s="10"/>
     </row>
     <row r="100" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="15"/>
@@ -7429,20 +7543,20 @@
         <v>97</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E100" s="8"/>
       <c r="F100" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I100" s="7" t="n">
         <v>1</v>
@@ -7454,13 +7568,13 @@
         <v>57885</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M100" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N100" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O100" s="10"/>
       <c r="P100" s="10"/>
@@ -7476,6 +7590,7 @@
       <c r="Z100" s="10"/>
       <c r="AA100" s="10"/>
       <c r="AB100" s="10"/>
+      <c r="AC100" s="10"/>
     </row>
     <row r="101" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="16"/>
@@ -7483,20 +7598,20 @@
         <v>98</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E101" s="13"/>
       <c r="F101" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I101" s="12" t="n">
         <v>2</v>
@@ -7508,13 +7623,13 @@
         <v>31324</v>
       </c>
       <c r="L101" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M101" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N101" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O101" s="10"/>
       <c r="P101" s="10"/>
@@ -7530,6 +7645,7 @@
       <c r="Z101" s="10"/>
       <c r="AA101" s="10"/>
       <c r="AB101" s="10"/>
+      <c r="AC101" s="10"/>
     </row>
     <row r="102" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="15"/>
@@ -7537,20 +7653,20 @@
         <v>99</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E102" s="8"/>
       <c r="F102" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I102" s="7" t="n">
         <v>3</v>
@@ -7562,13 +7678,13 @@
         <v>20241</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O102" s="10"/>
       <c r="P102" s="10"/>
@@ -7584,24 +7700,25 @@
       <c r="Z102" s="10"/>
       <c r="AA102" s="10"/>
       <c r="AB102" s="10"/>
+      <c r="AC102" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AB102"/>
+  <autoFilter ref="A3:AC102"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A1:AC1"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="O2:AB2"/>
+    <mergeCell ref="O2:AC2"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Never a yes/no question. Ask: &quot;How far into the month is the funding usually lasting right now?&quot;" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="O4:O102" type="list">
       <formula1>"accepting,waitlist,funds_exhausted,seasonal_closed,appointment_only,unknown"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Read the prefilled fact back as a statement." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="R4:R102" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Read the prefilled fact back as a statement." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="S4:S102" type="list">
       <formula1>"walk_in,phone,online,appointment"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Log every attempt, including the ones that fail." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="Y4:Y102" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Log every attempt, including the ones that fail." showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="Z4:Z102" type="list">
       <formula1>"reached,voicemail,no_answer,busy,wrong_number,callback_booked,refused,gatekeeper,disconnected"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7622,7 +7739,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -7631,174 +7748,174 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B1" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
         <v>441</v>
       </c>
-      <c r="B11" s="21" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="B12" s="19" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="21" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
         <v>453</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>442</v>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
         <v>460</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="23" t="s">
+      <c r="B22" s="19" t="s">
         <v>462</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18"/>
+      <c r="B25" s="19" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7806,7 +7923,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7814,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7822,7 +7939,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7830,7 +7947,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7838,7 +7955,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7846,7 +7963,7 @@
         <v>24</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7854,88 +7971,104 @@
         <v>25</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="23" t="s">
-        <v>474</v>
+      <c r="B38" s="23" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20" t="s">
-        <v>475</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
-        <v>476</v>
-      </c>
-      <c r="B40" s="24" t="str">
-        <f aca="false">COUNTA('Master List'!Y4:Y102)&amp;" of 99"</f>
-        <v>0 of 99</v>
+      <c r="A39" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="B41" s="24" t="n">
-        <f aca="false">COUNTIF('Master List'!Y4:Y102,"reached")</f>
-        <v>0</v>
+      <c r="A41" s="20" t="s">
+        <v>479</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="B42" s="24" t="n">
+        <v>480</v>
+      </c>
+      <c r="B42" s="24" t="str">
+        <f aca="false">COUNTA('Master List'!Z4:Z102)&amp;" of 99"</f>
+        <v>0 of 99</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="B43" s="24" t="n">
+        <f aca="false">COUNTIF('Master List'!Z4:Z102,"reached")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="B44" s="24" t="n">
         <f aca="false">COUNTIF('Master List'!O4:O102,"accepting")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="B43" s="25" t="str">
-        <f aca="false">IFERROR(COUNTIF('Master List'!Y4:Y102,"reached")/COUNTA('Master List'!Y4:Y102),"—")</f>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="B45" s="25" t="str">
+        <f aca="false">IFERROR(COUNTIF('Master List'!Z4:Z102,"reached")/COUNTA('Master List'!Z4:Z102),"—")</f>
         <v>—</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="26" t="s">
-        <v>480</v>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="26" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/data/call-sheets/CornerHelp-Master-Provider-List.xlsx
+++ b/data/call-sheets/CornerHelp-Master-Provider-List.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="487">
   <si>
     <t xml:space="preserve">CornerHelp — master provider call sheet · 99 organizations · all 254 Texas counties</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">SERVICE AREA — which ZIPs?</t>
+    <t xml:space="preserve">SERVICE AREA — whole county? which areas?</t>
   </si>
   <si>
     <t xml:space="preserve">Funding lasts until</t>
@@ -1334,10 +1334,16 @@
     <t xml:space="preserve">Only the YELLOW columns, from Status rightward. Navy columns are call context — leave them alone; they are how the row matches back to the database.</t>
   </si>
   <si>
-    <t xml:space="preserve">Service area is gating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A program does NOT publish on status alone. "Which ZIP codes do you actually cover?" is the second required question — the county list on this row is a crosswalk guess, and it is wrong: it gives every Harris agency 130 ZIPs when some serve five. Write what they say, verbatim, even if it is a neighbourhood name rather than ZIPs.</t>
+    <t xml:space="preserve">Service area — ask it their way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do NOT ask "which ZIP codes do you serve" — no intake worker can answer that. Ask: "Do you cover all of [county], or just part of it?" and then, if part: "Where do you have to turn people away for being outside your area?" Write down exactly what they say — "Spring Branch", "inside 610", "anywhere in the county". Converting that to ZIP codes is our job.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some rows need no answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agencies running CEAP, CSBG or WAP have their counties set by their TDHCA contract — the state publishes it and their answer cannot improve on it. Those rows are already publishable; skip the question. It matters for the pantries, churches and ministries, where a county is a guess.</t>
   </si>
   <si>
     <t xml:space="preserve">Blank beats guessed</t>
@@ -1445,7 +1451,7 @@
     <t xml:space="preserve">"People come in without the income for everybody in the house"</t>
   </si>
   <si>
-    <t xml:space="preserve">77042, 77057, 77063, 77077, 77082</t>
+    <t xml:space="preserve">not the whole county — west side, roughly Spring Branch out to Katy</t>
   </si>
   <si>
     <t xml:space="preserve">new intake system starting November</t>
@@ -2136,7 +2142,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
@@ -7739,7 +7745,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -7784,7 +7790,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
         <v>436</v>
       </c>
@@ -7800,7 +7806,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
         <v>440</v>
       </c>
@@ -7816,23 +7822,23 @@
         <v>443</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
         <v>444</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B11" s="19" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="21" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
         <v>448</v>
       </c>
@@ -7864,23 +7870,23 @@
         <v>455</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
         <v>456</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>445</v>
+      <c r="B18" s="19" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>457</v>
-      </c>
-      <c r="B20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="21" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
         <v>459</v>
       </c>
@@ -7888,7 +7894,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
         <v>461</v>
       </c>
@@ -7896,179 +7902,187 @@
         <v>462</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
         <v>463</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19" t="s">
+      <c r="B23" s="19" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="23" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
         <v>465</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
-        <v>479</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>445</v>
+      <c r="B40" s="23" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="s">
-        <v>480</v>
-      </c>
-      <c r="B42" s="24" t="str">
+      <c r="A42" s="20" t="s">
+        <v>481</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="B43" s="24" t="str">
         <f aca="false">COUNTA('Master List'!Z4:Z102)&amp;" of 99"</f>
         <v>0 of 99</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="B43" s="24" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="B44" s="24" t="n">
         <f aca="false">COUNTIF('Master List'!Z4:Z102,"reached")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="s">
-        <v>482</v>
-      </c>
-      <c r="B44" s="24" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="B45" s="24" t="n">
         <f aca="false">COUNTIF('Master List'!O4:O102,"accepting")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="B45" s="25" t="str">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="B46" s="25" t="str">
         <f aca="false">IFERROR(COUNTIF('Master List'!Z4:Z102,"reached")/COUNTA('Master List'!Z4:Z102),"—")</f>
         <v>—</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="26" t="s">
-        <v>484</v>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="26" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
